--- a/apps/backend/excel-data/issuereturn_library_migration.xlsx
+++ b/apps/backend/excel-data/issuereturn_library_migration.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="165">
   <si>
     <t>legacy_id</t>
   </si>
@@ -146,6 +146,366 @@
   </si>
   <si>
     <t>2026-05-06T08:54:55.674Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:13:08.842Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:13:14.234Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:13:15.076Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:13:16.076Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:13:16.901Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:13:18.014Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:13:22.660Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:13:27.190Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:13:33.396Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:13:34.773Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:13:44.736Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:13:54.356Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:13:59.851Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:14:06.973Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:14:19.246Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:14:27.076Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:14:33.813Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:14:35.110Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:14:45.165Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:14:49.882Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:15:04.063Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:15:10.456Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:15:22.908Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:15:29.719Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:15:39.637Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:15:40.799Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:15:41.926Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:15:42.860Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:15:52.744Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:15:59.260Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:16:14.098Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:16:20.425Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:16:25.760Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:16:32.426Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:16:40.607Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:16:45.455Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:16:55.941Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:17:00.946Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:17:06.788Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:17:13.440Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:17:23.904Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:17:35.603Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:17:37.503Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:17:46.157Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:17:52.628Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:18:00.781Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:18:05.767Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:18:10.689Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:18:11.491Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:18:12.383Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:18:23.172Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:18:29.123Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:18:34.533Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:18:39.589Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:18:44.161Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:18:48.526Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:18:53.667Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:18:58.526Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:19:05.160Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:19:10.834Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:19:17.608Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:19:22.564Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:19:24.229Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:19:32.107Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:19:35.976Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:19:43.634Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:19:44.452Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:19:45.248Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:19:49.155Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:19:49.995Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:19:51.001Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:19:54.726Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:19:55.639Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:20:06.910Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:20:13.899Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:20:24.102Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:20:29.856Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:20:35.060Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:20:35.974Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:20:37.009Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:20:43.619Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:20:55.226Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:21:02.814Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:21:07.886Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:21:12.396Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:21:17.453Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:21:23.774Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:21:29.608Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:21:44.903Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:21:45.808Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:21:55.306Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:21:56.264Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:22:05.599Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:22:13.678Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:22:19.984Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:22:20.761Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:22:30.951Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:22:35.829Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:22:40.607Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:22:50.455Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:22:54.717Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:22:59.738Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:23:09.138Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:23:10.075Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:23:10.991Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:23:15.260Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:23:28.375Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:23:29.796Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:23:40.981Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:23:46.688Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:23:51.381Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:24:00.605Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:24:08.406Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:24:13.673Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:24:20.232Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:24:27.948Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:24:31.797Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:24:36.932Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:24:42.042Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:24:46.909Z</t>
   </si>
 </sst>
 </file>
@@ -526,7 +886,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D157"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1047,6 +1407,1686 @@
         <v>44</v>
       </c>
     </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>36130</v>
+      </c>
+      <c r="B38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" t="s">
+        <v>14</v>
+      </c>
+      <c r="D38" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>36879</v>
+      </c>
+      <c r="B39" t="s">
+        <v>4</v>
+      </c>
+      <c r="C39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D39" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>36982</v>
+      </c>
+      <c r="B40" t="s">
+        <v>13</v>
+      </c>
+      <c r="C40" t="s">
+        <v>14</v>
+      </c>
+      <c r="D40" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>37243</v>
+      </c>
+      <c r="B41" t="s">
+        <v>13</v>
+      </c>
+      <c r="C41" t="s">
+        <v>14</v>
+      </c>
+      <c r="D41" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>38017</v>
+      </c>
+      <c r="B42" t="s">
+        <v>13</v>
+      </c>
+      <c r="C42" t="s">
+        <v>14</v>
+      </c>
+      <c r="D42" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>38021</v>
+      </c>
+      <c r="B43" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" t="s">
+        <v>14</v>
+      </c>
+      <c r="D43" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>39441</v>
+      </c>
+      <c r="B44" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" t="s">
+        <v>14</v>
+      </c>
+      <c r="D44" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>39797</v>
+      </c>
+      <c r="B45" t="s">
+        <v>4</v>
+      </c>
+      <c r="C45" t="s">
+        <v>5</v>
+      </c>
+      <c r="D45" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>39800</v>
+      </c>
+      <c r="B46" t="s">
+        <v>4</v>
+      </c>
+      <c r="C46" t="s">
+        <v>5</v>
+      </c>
+      <c r="D46" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>39804</v>
+      </c>
+      <c r="B47" t="s">
+        <v>13</v>
+      </c>
+      <c r="C47" t="s">
+        <v>14</v>
+      </c>
+      <c r="D47" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>39998</v>
+      </c>
+      <c r="B48" t="s">
+        <v>4</v>
+      </c>
+      <c r="C48" t="s">
+        <v>5</v>
+      </c>
+      <c r="D48" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>40023</v>
+      </c>
+      <c r="B49" t="s">
+        <v>4</v>
+      </c>
+      <c r="C49" t="s">
+        <v>5</v>
+      </c>
+      <c r="D49" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>40024</v>
+      </c>
+      <c r="B50" t="s">
+        <v>4</v>
+      </c>
+      <c r="C50" t="s">
+        <v>5</v>
+      </c>
+      <c r="D50" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>40025</v>
+      </c>
+      <c r="B51" t="s">
+        <v>4</v>
+      </c>
+      <c r="C51" t="s">
+        <v>5</v>
+      </c>
+      <c r="D51" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>40055</v>
+      </c>
+      <c r="B52" t="s">
+        <v>4</v>
+      </c>
+      <c r="C52" t="s">
+        <v>5</v>
+      </c>
+      <c r="D52" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>40701</v>
+      </c>
+      <c r="B53" t="s">
+        <v>4</v>
+      </c>
+      <c r="C53" t="s">
+        <v>5</v>
+      </c>
+      <c r="D53" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>40702</v>
+      </c>
+      <c r="B54" t="s">
+        <v>4</v>
+      </c>
+      <c r="C54" t="s">
+        <v>5</v>
+      </c>
+      <c r="D54" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>40721</v>
+      </c>
+      <c r="B55" t="s">
+        <v>13</v>
+      </c>
+      <c r="C55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D55" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>40722</v>
+      </c>
+      <c r="B56" t="s">
+        <v>4</v>
+      </c>
+      <c r="C56" t="s">
+        <v>5</v>
+      </c>
+      <c r="D56" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>40723</v>
+      </c>
+      <c r="B57" t="s">
+        <v>13</v>
+      </c>
+      <c r="C57" t="s">
+        <v>14</v>
+      </c>
+      <c r="D57" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>40753</v>
+      </c>
+      <c r="B58" t="s">
+        <v>4</v>
+      </c>
+      <c r="C58" t="s">
+        <v>5</v>
+      </c>
+      <c r="D58" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>40754</v>
+      </c>
+      <c r="B59" t="s">
+        <v>4</v>
+      </c>
+      <c r="C59" t="s">
+        <v>5</v>
+      </c>
+      <c r="D59" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>40800</v>
+      </c>
+      <c r="B60" t="s">
+        <v>4</v>
+      </c>
+      <c r="C60" t="s">
+        <v>5</v>
+      </c>
+      <c r="D60" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>40801</v>
+      </c>
+      <c r="B61" t="s">
+        <v>4</v>
+      </c>
+      <c r="C61" t="s">
+        <v>5</v>
+      </c>
+      <c r="D61" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>40802</v>
+      </c>
+      <c r="B62" t="s">
+        <v>4</v>
+      </c>
+      <c r="C62" t="s">
+        <v>5</v>
+      </c>
+      <c r="D62" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>40996</v>
+      </c>
+      <c r="B63" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" t="s">
+        <v>14</v>
+      </c>
+      <c r="D63" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>41181</v>
+      </c>
+      <c r="B64" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64" t="s">
+        <v>14</v>
+      </c>
+      <c r="D64" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>41182</v>
+      </c>
+      <c r="B65" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" t="s">
+        <v>14</v>
+      </c>
+      <c r="D65" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>41301</v>
+      </c>
+      <c r="B66" t="s">
+        <v>4</v>
+      </c>
+      <c r="C66" t="s">
+        <v>5</v>
+      </c>
+      <c r="D66" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>41302</v>
+      </c>
+      <c r="B67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C67" t="s">
+        <v>5</v>
+      </c>
+      <c r="D67" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>41406</v>
+      </c>
+      <c r="B68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C68" t="s">
+        <v>5</v>
+      </c>
+      <c r="D68" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>41436</v>
+      </c>
+      <c r="B69" t="s">
+        <v>4</v>
+      </c>
+      <c r="C69" t="s">
+        <v>5</v>
+      </c>
+      <c r="D69" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>41445</v>
+      </c>
+      <c r="B70" t="s">
+        <v>4</v>
+      </c>
+      <c r="C70" t="s">
+        <v>5</v>
+      </c>
+      <c r="D70" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>41456</v>
+      </c>
+      <c r="B71" t="s">
+        <v>4</v>
+      </c>
+      <c r="C71" t="s">
+        <v>5</v>
+      </c>
+      <c r="D71" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>41457</v>
+      </c>
+      <c r="B72" t="s">
+        <v>4</v>
+      </c>
+      <c r="C72" t="s">
+        <v>5</v>
+      </c>
+      <c r="D72" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>41458</v>
+      </c>
+      <c r="B73" t="s">
+        <v>4</v>
+      </c>
+      <c r="C73" t="s">
+        <v>5</v>
+      </c>
+      <c r="D73" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>41459</v>
+      </c>
+      <c r="B74" t="s">
+        <v>4</v>
+      </c>
+      <c r="C74" t="s">
+        <v>5</v>
+      </c>
+      <c r="D74" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>41566</v>
+      </c>
+      <c r="B75" t="s">
+        <v>4</v>
+      </c>
+      <c r="C75" t="s">
+        <v>5</v>
+      </c>
+      <c r="D75" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>41567</v>
+      </c>
+      <c r="B76" t="s">
+        <v>4</v>
+      </c>
+      <c r="C76" t="s">
+        <v>5</v>
+      </c>
+      <c r="D76" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>41568</v>
+      </c>
+      <c r="B77" t="s">
+        <v>4</v>
+      </c>
+      <c r="C77" t="s">
+        <v>5</v>
+      </c>
+      <c r="D77" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>41639</v>
+      </c>
+      <c r="B78" t="s">
+        <v>4</v>
+      </c>
+      <c r="C78" t="s">
+        <v>5</v>
+      </c>
+      <c r="D78" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>41640</v>
+      </c>
+      <c r="B79" t="s">
+        <v>4</v>
+      </c>
+      <c r="C79" t="s">
+        <v>5</v>
+      </c>
+      <c r="D79" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>41696</v>
+      </c>
+      <c r="B80" t="s">
+        <v>13</v>
+      </c>
+      <c r="C80" t="s">
+        <v>14</v>
+      </c>
+      <c r="D80" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>41821</v>
+      </c>
+      <c r="B81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C81" t="s">
+        <v>5</v>
+      </c>
+      <c r="D81" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>41824</v>
+      </c>
+      <c r="B82" t="s">
+        <v>4</v>
+      </c>
+      <c r="C82" t="s">
+        <v>5</v>
+      </c>
+      <c r="D82" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>41850</v>
+      </c>
+      <c r="B83" t="s">
+        <v>4</v>
+      </c>
+      <c r="C83" t="s">
+        <v>5</v>
+      </c>
+      <c r="D83" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>41851</v>
+      </c>
+      <c r="B84" t="s">
+        <v>4</v>
+      </c>
+      <c r="C84" t="s">
+        <v>5</v>
+      </c>
+      <c r="D84" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>41940</v>
+      </c>
+      <c r="B85" t="s">
+        <v>4</v>
+      </c>
+      <c r="C85" t="s">
+        <v>5</v>
+      </c>
+      <c r="D85" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>41952</v>
+      </c>
+      <c r="B86" t="s">
+        <v>13</v>
+      </c>
+      <c r="C86" t="s">
+        <v>14</v>
+      </c>
+      <c r="D86" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>41953</v>
+      </c>
+      <c r="B87" t="s">
+        <v>13</v>
+      </c>
+      <c r="C87" t="s">
+        <v>14</v>
+      </c>
+      <c r="D87" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>41970</v>
+      </c>
+      <c r="B88" t="s">
+        <v>4</v>
+      </c>
+      <c r="C88" t="s">
+        <v>5</v>
+      </c>
+      <c r="D88" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>41971</v>
+      </c>
+      <c r="B89" t="s">
+        <v>4</v>
+      </c>
+      <c r="C89" t="s">
+        <v>5</v>
+      </c>
+      <c r="D89" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>41972</v>
+      </c>
+      <c r="B90" t="s">
+        <v>4</v>
+      </c>
+      <c r="C90" t="s">
+        <v>5</v>
+      </c>
+      <c r="D90" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>41973</v>
+      </c>
+      <c r="B91" t="s">
+        <v>4</v>
+      </c>
+      <c r="C91" t="s">
+        <v>5</v>
+      </c>
+      <c r="D91" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>42066</v>
+      </c>
+      <c r="B92" t="s">
+        <v>4</v>
+      </c>
+      <c r="C92" t="s">
+        <v>5</v>
+      </c>
+      <c r="D92" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>42067</v>
+      </c>
+      <c r="B93" t="s">
+        <v>4</v>
+      </c>
+      <c r="C93" t="s">
+        <v>5</v>
+      </c>
+      <c r="D93" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>42068</v>
+      </c>
+      <c r="B94" t="s">
+        <v>4</v>
+      </c>
+      <c r="C94" t="s">
+        <v>5</v>
+      </c>
+      <c r="D94" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>42102</v>
+      </c>
+      <c r="B95" t="s">
+        <v>4</v>
+      </c>
+      <c r="C95" t="s">
+        <v>5</v>
+      </c>
+      <c r="D95" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>42120</v>
+      </c>
+      <c r="B96" t="s">
+        <v>4</v>
+      </c>
+      <c r="C96" t="s">
+        <v>5</v>
+      </c>
+      <c r="D96" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>42121</v>
+      </c>
+      <c r="B97" t="s">
+        <v>4</v>
+      </c>
+      <c r="C97" t="s">
+        <v>5</v>
+      </c>
+      <c r="D97" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>42258</v>
+      </c>
+      <c r="B98" t="s">
+        <v>4</v>
+      </c>
+      <c r="C98" t="s">
+        <v>5</v>
+      </c>
+      <c r="D98" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>42259</v>
+      </c>
+      <c r="B99" t="s">
+        <v>4</v>
+      </c>
+      <c r="C99" t="s">
+        <v>5</v>
+      </c>
+      <c r="D99" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>42439</v>
+      </c>
+      <c r="B100" t="s">
+        <v>13</v>
+      </c>
+      <c r="C100" t="s">
+        <v>14</v>
+      </c>
+      <c r="D100" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>42526</v>
+      </c>
+      <c r="B101" t="s">
+        <v>4</v>
+      </c>
+      <c r="C101" t="s">
+        <v>5</v>
+      </c>
+      <c r="D101" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>42527</v>
+      </c>
+      <c r="B102" t="s">
+        <v>4</v>
+      </c>
+      <c r="C102" t="s">
+        <v>5</v>
+      </c>
+      <c r="D102" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>42528</v>
+      </c>
+      <c r="B103" t="s">
+        <v>4</v>
+      </c>
+      <c r="C103" t="s">
+        <v>5</v>
+      </c>
+      <c r="D103" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>42669</v>
+      </c>
+      <c r="B104" t="s">
+        <v>13</v>
+      </c>
+      <c r="C104" t="s">
+        <v>14</v>
+      </c>
+      <c r="D104" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>42802</v>
+      </c>
+      <c r="B105" t="s">
+        <v>13</v>
+      </c>
+      <c r="C105" t="s">
+        <v>14</v>
+      </c>
+      <c r="D105" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>42852</v>
+      </c>
+      <c r="B106" t="s">
+        <v>4</v>
+      </c>
+      <c r="C106" t="s">
+        <v>5</v>
+      </c>
+      <c r="D106" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>42854</v>
+      </c>
+      <c r="B107" t="s">
+        <v>13</v>
+      </c>
+      <c r="C107" t="s">
+        <v>14</v>
+      </c>
+      <c r="D107" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>42855</v>
+      </c>
+      <c r="B108" t="s">
+        <v>13</v>
+      </c>
+      <c r="C108" t="s">
+        <v>14</v>
+      </c>
+      <c r="D108" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>42856</v>
+      </c>
+      <c r="B109" t="s">
+        <v>4</v>
+      </c>
+      <c r="C109" t="s">
+        <v>5</v>
+      </c>
+      <c r="D109" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>43251</v>
+      </c>
+      <c r="B110" t="s">
+        <v>13</v>
+      </c>
+      <c r="C110" t="s">
+        <v>14</v>
+      </c>
+      <c r="D110" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>43324</v>
+      </c>
+      <c r="B111" t="s">
+        <v>4</v>
+      </c>
+      <c r="C111" t="s">
+        <v>5</v>
+      </c>
+      <c r="D111" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>43333</v>
+      </c>
+      <c r="B112" t="s">
+        <v>4</v>
+      </c>
+      <c r="C112" t="s">
+        <v>5</v>
+      </c>
+      <c r="D112" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>43439</v>
+      </c>
+      <c r="B113" t="s">
+        <v>4</v>
+      </c>
+      <c r="C113" t="s">
+        <v>5</v>
+      </c>
+      <c r="D113" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>43440</v>
+      </c>
+      <c r="B114" t="s">
+        <v>4</v>
+      </c>
+      <c r="C114" t="s">
+        <v>5</v>
+      </c>
+      <c r="D114" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>43441</v>
+      </c>
+      <c r="B115" t="s">
+        <v>4</v>
+      </c>
+      <c r="C115" t="s">
+        <v>5</v>
+      </c>
+      <c r="D115" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>43620</v>
+      </c>
+      <c r="B116" t="s">
+        <v>13</v>
+      </c>
+      <c r="C116" t="s">
+        <v>14</v>
+      </c>
+      <c r="D116" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>43622</v>
+      </c>
+      <c r="B117" t="s">
+        <v>13</v>
+      </c>
+      <c r="C117" t="s">
+        <v>14</v>
+      </c>
+      <c r="D117" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>43866</v>
+      </c>
+      <c r="B118" t="s">
+        <v>4</v>
+      </c>
+      <c r="C118" t="s">
+        <v>5</v>
+      </c>
+      <c r="D118" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>43867</v>
+      </c>
+      <c r="B119" t="s">
+        <v>4</v>
+      </c>
+      <c r="C119" t="s">
+        <v>5</v>
+      </c>
+      <c r="D119" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>43878</v>
+      </c>
+      <c r="B120" t="s">
+        <v>4</v>
+      </c>
+      <c r="C120" t="s">
+        <v>5</v>
+      </c>
+      <c r="D120" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>43879</v>
+      </c>
+      <c r="B121" t="s">
+        <v>4</v>
+      </c>
+      <c r="C121" t="s">
+        <v>5</v>
+      </c>
+      <c r="D121" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>43934</v>
+      </c>
+      <c r="B122" t="s">
+        <v>4</v>
+      </c>
+      <c r="C122" t="s">
+        <v>5</v>
+      </c>
+      <c r="D122" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>43941</v>
+      </c>
+      <c r="B123" t="s">
+        <v>4</v>
+      </c>
+      <c r="C123" t="s">
+        <v>5</v>
+      </c>
+      <c r="D123" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>44078</v>
+      </c>
+      <c r="B124" t="s">
+        <v>4</v>
+      </c>
+      <c r="C124" t="s">
+        <v>5</v>
+      </c>
+      <c r="D124" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>44079</v>
+      </c>
+      <c r="B125" t="s">
+        <v>4</v>
+      </c>
+      <c r="C125" t="s">
+        <v>5</v>
+      </c>
+      <c r="D125" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>44341</v>
+      </c>
+      <c r="B126" t="s">
+        <v>4</v>
+      </c>
+      <c r="C126" t="s">
+        <v>5</v>
+      </c>
+      <c r="D126" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>44376</v>
+      </c>
+      <c r="B127" t="s">
+        <v>13</v>
+      </c>
+      <c r="C127" t="s">
+        <v>14</v>
+      </c>
+      <c r="D127" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>44456</v>
+      </c>
+      <c r="B128" t="s">
+        <v>4</v>
+      </c>
+      <c r="C128" t="s">
+        <v>5</v>
+      </c>
+      <c r="D128" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>44632</v>
+      </c>
+      <c r="B129" t="s">
+        <v>13</v>
+      </c>
+      <c r="C129" t="s">
+        <v>14</v>
+      </c>
+      <c r="D129" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>44633</v>
+      </c>
+      <c r="B130" t="s">
+        <v>4</v>
+      </c>
+      <c r="C130" t="s">
+        <v>5</v>
+      </c>
+      <c r="D130" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>44652</v>
+      </c>
+      <c r="B131" t="s">
+        <v>4</v>
+      </c>
+      <c r="C131" t="s">
+        <v>5</v>
+      </c>
+      <c r="D131" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>44653</v>
+      </c>
+      <c r="B132" t="s">
+        <v>4</v>
+      </c>
+      <c r="C132" t="s">
+        <v>5</v>
+      </c>
+      <c r="D132" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>44662</v>
+      </c>
+      <c r="B133" t="s">
+        <v>13</v>
+      </c>
+      <c r="C133" t="s">
+        <v>14</v>
+      </c>
+      <c r="D133" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>44667</v>
+      </c>
+      <c r="B134" t="s">
+        <v>4</v>
+      </c>
+      <c r="C134" t="s">
+        <v>5</v>
+      </c>
+      <c r="D134" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>44668</v>
+      </c>
+      <c r="B135" t="s">
+        <v>4</v>
+      </c>
+      <c r="C135" t="s">
+        <v>5</v>
+      </c>
+      <c r="D135" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>44671</v>
+      </c>
+      <c r="B136" t="s">
+        <v>4</v>
+      </c>
+      <c r="C136" t="s">
+        <v>5</v>
+      </c>
+      <c r="D136" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>44678</v>
+      </c>
+      <c r="B137" t="s">
+        <v>4</v>
+      </c>
+      <c r="C137" t="s">
+        <v>5</v>
+      </c>
+      <c r="D137" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>44679</v>
+      </c>
+      <c r="B138" t="s">
+        <v>4</v>
+      </c>
+      <c r="C138" t="s">
+        <v>5</v>
+      </c>
+      <c r="D138" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>44680</v>
+      </c>
+      <c r="B139" t="s">
+        <v>4</v>
+      </c>
+      <c r="C139" t="s">
+        <v>5</v>
+      </c>
+      <c r="D139" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>44699</v>
+      </c>
+      <c r="B140" t="s">
+        <v>4</v>
+      </c>
+      <c r="C140" t="s">
+        <v>5</v>
+      </c>
+      <c r="D140" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>44700</v>
+      </c>
+      <c r="B141" t="s">
+        <v>13</v>
+      </c>
+      <c r="C141" t="s">
+        <v>14</v>
+      </c>
+      <c r="D141" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>44711</v>
+      </c>
+      <c r="B142" t="s">
+        <v>13</v>
+      </c>
+      <c r="C142" t="s">
+        <v>14</v>
+      </c>
+      <c r="D142" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>44741</v>
+      </c>
+      <c r="B143" t="s">
+        <v>4</v>
+      </c>
+      <c r="C143" t="s">
+        <v>5</v>
+      </c>
+      <c r="D143" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>44827</v>
+      </c>
+      <c r="B144" t="s">
+        <v>4</v>
+      </c>
+      <c r="C144" t="s">
+        <v>5</v>
+      </c>
+      <c r="D144" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>44859</v>
+      </c>
+      <c r="B145" t="s">
+        <v>13</v>
+      </c>
+      <c r="C145" t="s">
+        <v>14</v>
+      </c>
+      <c r="D145" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>44871</v>
+      </c>
+      <c r="B146" t="s">
+        <v>4</v>
+      </c>
+      <c r="C146" t="s">
+        <v>5</v>
+      </c>
+      <c r="D146" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>44918</v>
+      </c>
+      <c r="B147" t="s">
+        <v>4</v>
+      </c>
+      <c r="C147" t="s">
+        <v>5</v>
+      </c>
+      <c r="D147" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>44919</v>
+      </c>
+      <c r="B148" t="s">
+        <v>4</v>
+      </c>
+      <c r="C148" t="s">
+        <v>5</v>
+      </c>
+      <c r="D148" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>45055</v>
+      </c>
+      <c r="B149" t="s">
+        <v>4</v>
+      </c>
+      <c r="C149" t="s">
+        <v>5</v>
+      </c>
+      <c r="D149" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>45079</v>
+      </c>
+      <c r="B150" t="s">
+        <v>4</v>
+      </c>
+      <c r="C150" t="s">
+        <v>5</v>
+      </c>
+      <c r="D150" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>45080</v>
+      </c>
+      <c r="B151" t="s">
+        <v>4</v>
+      </c>
+      <c r="C151" t="s">
+        <v>5</v>
+      </c>
+      <c r="D151" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>45081</v>
+      </c>
+      <c r="B152" t="s">
+        <v>4</v>
+      </c>
+      <c r="C152" t="s">
+        <v>5</v>
+      </c>
+      <c r="D152" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>45082</v>
+      </c>
+      <c r="B153" t="s">
+        <v>4</v>
+      </c>
+      <c r="C153" t="s">
+        <v>5</v>
+      </c>
+      <c r="D153" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>45097</v>
+      </c>
+      <c r="B154" t="s">
+        <v>4</v>
+      </c>
+      <c r="C154" t="s">
+        <v>5</v>
+      </c>
+      <c r="D154" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>45242</v>
+      </c>
+      <c r="B155" t="s">
+        <v>4</v>
+      </c>
+      <c r="C155" t="s">
+        <v>5</v>
+      </c>
+      <c r="D155" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>45266</v>
+      </c>
+      <c r="B156" t="s">
+        <v>4</v>
+      </c>
+      <c r="C156" t="s">
+        <v>5</v>
+      </c>
+      <c r="D156" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>45276</v>
+      </c>
+      <c r="B157" t="s">
+        <v>4</v>
+      </c>
+      <c r="C157" t="s">
+        <v>5</v>
+      </c>
+      <c r="D157" t="s">
+        <v>164</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/apps/backend/excel-data/issuereturn_library_migration.xlsx
+++ b/apps/backend/excel-data/issuereturn_library_migration.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="171">
   <si>
     <t>legacy_id</t>
   </si>
@@ -506,6 +506,24 @@
   </si>
   <si>
     <t>2026-05-07T06:24:46.909Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:24:52.610Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:25:02.086Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:25:09.474Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:25:20.391Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:25:25.870Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:25:30.900Z</t>
   </si>
 </sst>
 </file>
@@ -886,7 +904,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D157"/>
+  <dimension ref="A1:D163"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3087,6 +3105,90 @@
         <v>164</v>
       </c>
     </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>45345</v>
+      </c>
+      <c r="B158" t="s">
+        <v>4</v>
+      </c>
+      <c r="C158" t="s">
+        <v>5</v>
+      </c>
+      <c r="D158" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <v>45395</v>
+      </c>
+      <c r="B159" t="s">
+        <v>4</v>
+      </c>
+      <c r="C159" t="s">
+        <v>5</v>
+      </c>
+      <c r="D159" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <v>45396</v>
+      </c>
+      <c r="B160" t="s">
+        <v>4</v>
+      </c>
+      <c r="C160" t="s">
+        <v>5</v>
+      </c>
+      <c r="D160" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>45435</v>
+      </c>
+      <c r="B161" t="s">
+        <v>4</v>
+      </c>
+      <c r="C161" t="s">
+        <v>5</v>
+      </c>
+      <c r="D161" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>45436</v>
+      </c>
+      <c r="B162" t="s">
+        <v>4</v>
+      </c>
+      <c r="C162" t="s">
+        <v>5</v>
+      </c>
+      <c r="D162" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>45444</v>
+      </c>
+      <c r="B163" t="s">
+        <v>4</v>
+      </c>
+      <c r="C163" t="s">
+        <v>5</v>
+      </c>
+      <c r="D163" t="s">
+        <v>170</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/apps/backend/excel-data/issuereturn_library_migration.xlsx
+++ b/apps/backend/excel-data/issuereturn_library_migration.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1870" uniqueCount="631">
   <si>
     <t>legacy_id</t>
   </si>
@@ -524,6 +524,1386 @@
   </si>
   <si>
     <t>2026-05-07T06:25:30.900Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:25:38.666Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:25:46.069Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:25:54.310Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:26:01.961Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:26:06.450Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:26:11.589Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:26:17.373Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:26:24.639Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:26:30.685Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:26:39.527Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:26:46.104Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:26:53.027Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:26:53.913Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:27:05.577Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:27:10.309Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:27:21.994Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:27:23.126Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:27:25.123Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:27:39.367Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:27:43.672Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:27:48.057Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:27:52.742Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:27:56.962Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:28:05.018Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:28:11.322Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:28:16.099Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:28:22.884Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:28:29.314Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:28:33.088Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:28:33.916Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:28:34.702Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:28:39.976Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:28:44.915Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:28:45.895Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:28:52.565Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:28:59.553Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:29:08.107Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:29:17.768Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:29:25.370Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:29:34.629Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:29:46.511Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:29:55.841Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:30:01.862Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:30:08.827Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:30:15.085Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:30:15.885Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:30:17.073Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:30:21.655Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:30:22.842Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:30:24.180Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:30:31.674Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:30:41.112Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:30:44.946Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:30:54.440Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:31:00.512Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:31:01.385Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:31:10.039Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:31:18.485Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:31:19.516Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:31:26.993Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:31:33.587Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:31:50.296Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:32:03.967Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:32:07.905Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:32:15.736Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:32:24.436Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:32:28.573Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:32:35.939Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:32:43.751Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:32:45.539Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:32:54.001Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:32:58.443Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:33:10.945Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:33:11.853Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:33:18.517Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:33:24.176Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:33:27.790Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:33:32.877Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:33:38.503Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:33:42.527Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:33:46.427Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:33:52.113Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:33:56.513Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:34:01.002Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:34:08.028Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:34:15.216Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:34:21.171Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:34:28.144Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:34:34.112Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:34:39.520Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:34:45.962Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:34:53.167Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:35:01.431Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:35:08.034Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:35:20.913Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:35:21.874Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:35:28.938Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:35:32.765Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:35:39.697Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:35:44.004Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:35:53.658Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:35:57.301Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:36:09.994Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:36:15.581Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:36:23.224Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:36:24.182Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:36:28.888Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:36:35.247Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:36:43.379Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:36:45.049Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:36:51.982Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:36:52.942Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:37:00.305Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:37:06.546Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:37:12.783Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:37:14.298Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:37:20.655Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:37:27.142Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:37:32.344Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:37:48.523Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:37:49.464Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:37:50.446Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:37:51.443Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:37:52.722Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:37:53.789Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:37:54.806Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:38:01.854Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:38:09.545Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:38:17.399Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:38:23.209Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:38:24.288Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:38:31.470Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:38:36.079Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:38:43.344Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:38:50.585Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:38:51.654Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:38:58.202Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:39:05.218Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:39:11.803Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:39:18.656Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:39:30.234Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:39:39.013Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:39:43.126Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:39:51.299Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:39:57.699Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:40:04.008Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:40:10.058Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:40:17.142Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:40:27.593Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:40:33.566Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:40:38.811Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:40:45.279Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:40:52.215Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:40:58.337Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:40:59.695Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:41:06.593Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:41:11.315Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:41:13.214Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:41:18.307Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:41:25.096Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:41:30.098Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:41:34.845Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:41:47.186Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:41:58.041Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:42:02.085Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:42:08.683Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:42:16.396Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:42:24.388Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:42:25.676Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:42:27.163Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:42:28.473Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:42:32.916Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:42:34.598Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:42:36.044Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:42:48.622Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:42:57.306Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:43:06.222Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:43:15.343Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:43:22.345Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:43:34.111Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:43:35.328Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:43:36.689Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:43:40.924Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:43:41.965Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:43:42.912Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:43:43.823Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:43:44.707Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:43:50.073Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:44:11.174Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:44:21.407Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:44:24.653Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:44:35.463Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:44:41.173Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:44:47.609Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:44:58.769Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:45:04.103Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:45:15.078Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:45:23.631Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:45:33.878Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:45:42.032Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:45:49.717Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:45:53.286Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:46:04.141Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:46:11.160Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:46:23.539Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:46:32.719Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:46:36.158Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:46:42.640Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:46:51.771Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:46:58.988Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:47:04.376Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:47:06.394Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:47:13.593Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:47:25.811Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:47:31.626Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:47:36.504Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:47:45.370Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:47:46.986Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:47:50.201Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:47:55.719Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:48:04.367Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:48:12.033Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:48:13.489Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:48:14.540Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:48:20.778Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:48:26.976Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:48:33.050Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:48:40.635Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:48:45.766Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:48:53.546Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:49:02.303Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:49:11.070Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:49:17.750Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:49:24.862Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:49:32.574Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:49:37.135Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:49:45.321Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:49:46.807Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:49:59.529Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:50:06.899Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:50:12.113Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:50:19.707Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:50:21.555Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:50:29.274Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:50:36.285Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:50:41.458Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:50:46.445Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:50:48.276Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:50:54.765Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:51:02.139Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:51:04.192Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:51:18.519Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:51:26.887Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:51:28.367Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:51:29.938Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:51:31.417Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:51:32.846Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:51:38.240Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:51:43.961Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:51:53.925Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:51:59.445Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:52:04.373Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:52:12.672Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:52:21.243Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:52:25.835Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:52:32.870Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:52:37.355Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:52:43.218Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:52:51.586Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:53:00.480Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:53:04.413Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:53:12.983Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:53:15.673Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:53:23.324Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:53:29.743Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:53:38.470Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:53:49.569Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:53:54.606Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:54:03.267Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:54:09.326Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:54:16.420Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:54:23.217Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:54:29.221Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:54:34.701Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:54:42.750Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:54:43.578Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:54:53.281Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:55:01.267Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:55:09.465Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:55:10.887Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:55:12.096Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:55:13.314Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:55:14.250Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:55:15.212Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:55:16.529Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:55:17.715Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:55:19.029Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:55:25.836Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:55:35.792Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:55:36.998Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:55:38.187Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:55:44.776Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:55:58.166Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:56:10.260Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:56:15.088Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:56:25.045Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:56:31.838Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:56:37.261Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:56:38.508Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:56:39.734Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:56:50.228Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:56:55.082Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:57:02.196Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:57:08.201Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:57:13.425Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:57:23.495Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:57:29.194Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:57:37.126Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:57:41.972Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:57:47.739Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:57:52.820Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:57:58.483Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:58:04.937Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:58:10.905Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:58:11.744Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:58:19.747Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:58:20.810Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:58:23.481Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:58:30.052Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:58:36.687Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:58:44.347Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:58:50.140Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:59:06.624Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:59:16.038Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:59:27.650Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:59:36.703Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:59:42.264Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:59:51.304Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T06:59:56.424Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:00:02.537Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:00:09.043Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:00:13.591Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:00:19.267Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:00:26.313Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:00:32.644Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:00:39.158Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:00:40.005Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:00:44.144Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:00:49.966Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:00:56.578Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:01:04.666Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:01:09.407Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:01:23.164Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:01:30.988Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:01:37.461Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:01:45.638Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:01:53.371Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:01:54.602Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:01:55.780Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:02:01.784Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:02:10.491Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:02:18.243Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:02:23.540Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:02:32.174Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:02:49.625Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:02:57.051Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:03:06.295Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:03:12.268Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:03:13.246Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:03:19.508Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:03:20.511Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:03:21.422Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:03:28.531Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:03:33.750Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:03:46.712Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:03:51.658Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:03:58.190Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:04:07.882Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:04:18.048Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:04:25.898Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:04:32.350Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:04:37.410Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:04:45.639Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:04:51.105Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:04:55.510Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:05:02.900Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:05:11.209Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:05:21.981Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:05:27.889Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:05:29.123Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:05:38.055Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:05:43.857Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:05:49.696Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:05:56.640Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:06:02.805Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:06:08.924Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:06:15.121Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:06:19.806Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:06:31.085Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:06:38.652Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:06:45.678Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:06:46.467Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:06:53.867Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:07:02.617Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:07:10.899Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:07:19.485Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:07:25.386Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:07:31.577Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:07:38.798Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:07:45.834Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:07:54.152Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:08:02.459Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:08:08.729Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:08:15.079Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:08:21.151Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:08:27.968Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:08:33.114Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:08:38.207Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:08:44.222Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:08:51.553Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:08:58.340Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:09:04.850Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:09:10.009Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:09:16.912Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:09:22.928Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:09:32.082Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:09:39.584Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:09:51.224Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:09:59.834Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:10:07.245Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:10:13.266Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:10:20.110Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:10:26.190Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:10:27.139Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:10:28.006Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:10:33.662Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:10:42.024Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:10:49.799Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:10:50.655Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:11:00.124Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:11:06.171Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:11:07.420Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:11:25.017Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:11:33.743Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:11:37.302Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:11:50.788Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:12:01.142Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:12:12.436Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:12:14.552Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:12:16.875Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:12:18.451Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:12:24.678Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:12:25.487Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:12:32.054Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:12:40.185Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:12:55.040Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:13:07.355Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:13:15.856Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:13:25.404Z</t>
+  </si>
+  <si>
+    <t>2026-05-07T07:13:41.357Z</t>
   </si>
 </sst>
 </file>
@@ -904,7 +2284,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D163"/>
+  <dimension ref="A1:D623"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3189,6 +4569,6446 @@
         <v>170</v>
       </c>
     </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <v>45546</v>
+      </c>
+      <c r="B164" t="s">
+        <v>4</v>
+      </c>
+      <c r="C164" t="s">
+        <v>5</v>
+      </c>
+      <c r="D164" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>45547</v>
+      </c>
+      <c r="B165" t="s">
+        <v>4</v>
+      </c>
+      <c r="C165" t="s">
+        <v>5</v>
+      </c>
+      <c r="D165" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>45600</v>
+      </c>
+      <c r="B166" t="s">
+        <v>4</v>
+      </c>
+      <c r="C166" t="s">
+        <v>5</v>
+      </c>
+      <c r="D166" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <v>45611</v>
+      </c>
+      <c r="B167" t="s">
+        <v>4</v>
+      </c>
+      <c r="C167" t="s">
+        <v>5</v>
+      </c>
+      <c r="D167" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>45612</v>
+      </c>
+      <c r="B168" t="s">
+        <v>4</v>
+      </c>
+      <c r="C168" t="s">
+        <v>5</v>
+      </c>
+      <c r="D168" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>45655</v>
+      </c>
+      <c r="B169" t="s">
+        <v>4</v>
+      </c>
+      <c r="C169" t="s">
+        <v>5</v>
+      </c>
+      <c r="D169" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>45656</v>
+      </c>
+      <c r="B170" t="s">
+        <v>4</v>
+      </c>
+      <c r="C170" t="s">
+        <v>5</v>
+      </c>
+      <c r="D170" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>45680</v>
+      </c>
+      <c r="B171" t="s">
+        <v>4</v>
+      </c>
+      <c r="C171" t="s">
+        <v>5</v>
+      </c>
+      <c r="D171" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>45806</v>
+      </c>
+      <c r="B172" t="s">
+        <v>4</v>
+      </c>
+      <c r="C172" t="s">
+        <v>5</v>
+      </c>
+      <c r="D172" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>45879</v>
+      </c>
+      <c r="B173" t="s">
+        <v>4</v>
+      </c>
+      <c r="C173" t="s">
+        <v>5</v>
+      </c>
+      <c r="D173" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>45880</v>
+      </c>
+      <c r="B174" t="s">
+        <v>4</v>
+      </c>
+      <c r="C174" t="s">
+        <v>5</v>
+      </c>
+      <c r="D174" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>45881</v>
+      </c>
+      <c r="B175" t="s">
+        <v>4</v>
+      </c>
+      <c r="C175" t="s">
+        <v>5</v>
+      </c>
+      <c r="D175" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>46018</v>
+      </c>
+      <c r="B176" t="s">
+        <v>13</v>
+      </c>
+      <c r="C176" t="s">
+        <v>14</v>
+      </c>
+      <c r="D176" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>46111</v>
+      </c>
+      <c r="B177" t="s">
+        <v>4</v>
+      </c>
+      <c r="C177" t="s">
+        <v>5</v>
+      </c>
+      <c r="D177" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>46169</v>
+      </c>
+      <c r="B178" t="s">
+        <v>4</v>
+      </c>
+      <c r="C178" t="s">
+        <v>5</v>
+      </c>
+      <c r="D178" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>46212</v>
+      </c>
+      <c r="B179" t="s">
+        <v>4</v>
+      </c>
+      <c r="C179" t="s">
+        <v>5</v>
+      </c>
+      <c r="D179" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <v>46402</v>
+      </c>
+      <c r="B180" t="s">
+        <v>13</v>
+      </c>
+      <c r="C180" t="s">
+        <v>14</v>
+      </c>
+      <c r="D180" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>46413</v>
+      </c>
+      <c r="B181" t="s">
+        <v>13</v>
+      </c>
+      <c r="C181" t="s">
+        <v>14</v>
+      </c>
+      <c r="D181" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A182">
+        <v>46559</v>
+      </c>
+      <c r="B182" t="s">
+        <v>4</v>
+      </c>
+      <c r="C182" t="s">
+        <v>5</v>
+      </c>
+      <c r="D182" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A183">
+        <v>46590</v>
+      </c>
+      <c r="B183" t="s">
+        <v>4</v>
+      </c>
+      <c r="C183" t="s">
+        <v>5</v>
+      </c>
+      <c r="D183" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A184">
+        <v>46591</v>
+      </c>
+      <c r="B184" t="s">
+        <v>4</v>
+      </c>
+      <c r="C184" t="s">
+        <v>5</v>
+      </c>
+      <c r="D184" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A185">
+        <v>46592</v>
+      </c>
+      <c r="B185" t="s">
+        <v>4</v>
+      </c>
+      <c r="C185" t="s">
+        <v>5</v>
+      </c>
+      <c r="D185" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A186">
+        <v>46593</v>
+      </c>
+      <c r="B186" t="s">
+        <v>4</v>
+      </c>
+      <c r="C186" t="s">
+        <v>5</v>
+      </c>
+      <c r="D186" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A187">
+        <v>46681</v>
+      </c>
+      <c r="B187" t="s">
+        <v>4</v>
+      </c>
+      <c r="C187" t="s">
+        <v>5</v>
+      </c>
+      <c r="D187" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A188">
+        <v>46800</v>
+      </c>
+      <c r="B188" t="s">
+        <v>4</v>
+      </c>
+      <c r="C188" t="s">
+        <v>5</v>
+      </c>
+      <c r="D188" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A189">
+        <v>46863</v>
+      </c>
+      <c r="B189" t="s">
+        <v>4</v>
+      </c>
+      <c r="C189" t="s">
+        <v>5</v>
+      </c>
+      <c r="D189" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A190">
+        <v>46869</v>
+      </c>
+      <c r="B190" t="s">
+        <v>4</v>
+      </c>
+      <c r="C190" t="s">
+        <v>5</v>
+      </c>
+      <c r="D190" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A191">
+        <v>46870</v>
+      </c>
+      <c r="B191" t="s">
+        <v>4</v>
+      </c>
+      <c r="C191" t="s">
+        <v>5</v>
+      </c>
+      <c r="D191" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A192">
+        <v>47122</v>
+      </c>
+      <c r="B192" t="s">
+        <v>4</v>
+      </c>
+      <c r="C192" t="s">
+        <v>5</v>
+      </c>
+      <c r="D192" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A193">
+        <v>47141</v>
+      </c>
+      <c r="B193" t="s">
+        <v>13</v>
+      </c>
+      <c r="C193" t="s">
+        <v>14</v>
+      </c>
+      <c r="D193" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A194">
+        <v>47199</v>
+      </c>
+      <c r="B194" t="s">
+        <v>13</v>
+      </c>
+      <c r="C194" t="s">
+        <v>14</v>
+      </c>
+      <c r="D194" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A195">
+        <v>47266</v>
+      </c>
+      <c r="B195" t="s">
+        <v>4</v>
+      </c>
+      <c r="C195" t="s">
+        <v>5</v>
+      </c>
+      <c r="D195" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A196">
+        <v>47267</v>
+      </c>
+      <c r="B196" t="s">
+        <v>4</v>
+      </c>
+      <c r="C196" t="s">
+        <v>5</v>
+      </c>
+      <c r="D196" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A197">
+        <v>47485</v>
+      </c>
+      <c r="B197" t="s">
+        <v>13</v>
+      </c>
+      <c r="C197" t="s">
+        <v>14</v>
+      </c>
+      <c r="D197" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A198">
+        <v>47543</v>
+      </c>
+      <c r="B198" t="s">
+        <v>4</v>
+      </c>
+      <c r="C198" t="s">
+        <v>5</v>
+      </c>
+      <c r="D198" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A199">
+        <v>47580</v>
+      </c>
+      <c r="B199" t="s">
+        <v>4</v>
+      </c>
+      <c r="C199" t="s">
+        <v>5</v>
+      </c>
+      <c r="D199" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A200">
+        <v>47711</v>
+      </c>
+      <c r="B200" t="s">
+        <v>4</v>
+      </c>
+      <c r="C200" t="s">
+        <v>5</v>
+      </c>
+      <c r="D200" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A201">
+        <v>47717</v>
+      </c>
+      <c r="B201" t="s">
+        <v>4</v>
+      </c>
+      <c r="C201" t="s">
+        <v>5</v>
+      </c>
+      <c r="D201" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A202">
+        <v>47840</v>
+      </c>
+      <c r="B202" t="s">
+        <v>4</v>
+      </c>
+      <c r="C202" t="s">
+        <v>5</v>
+      </c>
+      <c r="D202" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A203">
+        <v>47873</v>
+      </c>
+      <c r="B203" t="s">
+        <v>4</v>
+      </c>
+      <c r="C203" t="s">
+        <v>5</v>
+      </c>
+      <c r="D203" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A204">
+        <v>47874</v>
+      </c>
+      <c r="B204" t="s">
+        <v>4</v>
+      </c>
+      <c r="C204" t="s">
+        <v>5</v>
+      </c>
+      <c r="D204" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A205">
+        <v>47891</v>
+      </c>
+      <c r="B205" t="s">
+        <v>4</v>
+      </c>
+      <c r="C205" t="s">
+        <v>5</v>
+      </c>
+      <c r="D205" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A206">
+        <v>47892</v>
+      </c>
+      <c r="B206" t="s">
+        <v>4</v>
+      </c>
+      <c r="C206" t="s">
+        <v>5</v>
+      </c>
+      <c r="D206" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A207">
+        <v>47893</v>
+      </c>
+      <c r="B207" t="s">
+        <v>4</v>
+      </c>
+      <c r="C207" t="s">
+        <v>5</v>
+      </c>
+      <c r="D207" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A208">
+        <v>47953</v>
+      </c>
+      <c r="B208" t="s">
+        <v>4</v>
+      </c>
+      <c r="C208" t="s">
+        <v>5</v>
+      </c>
+      <c r="D208" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A209">
+        <v>48002</v>
+      </c>
+      <c r="B209" t="s">
+        <v>13</v>
+      </c>
+      <c r="C209" t="s">
+        <v>14</v>
+      </c>
+      <c r="D209" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A210">
+        <v>48003</v>
+      </c>
+      <c r="B210" t="s">
+        <v>13</v>
+      </c>
+      <c r="C210" t="s">
+        <v>14</v>
+      </c>
+      <c r="D210" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A211">
+        <v>48029</v>
+      </c>
+      <c r="B211" t="s">
+        <v>4</v>
+      </c>
+      <c r="C211" t="s">
+        <v>5</v>
+      </c>
+      <c r="D211" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A212">
+        <v>48079</v>
+      </c>
+      <c r="B212" t="s">
+        <v>13</v>
+      </c>
+      <c r="C212" t="s">
+        <v>14</v>
+      </c>
+      <c r="D212" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A213">
+        <v>48080</v>
+      </c>
+      <c r="B213" t="s">
+        <v>13</v>
+      </c>
+      <c r="C213" t="s">
+        <v>14</v>
+      </c>
+      <c r="D213" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A214">
+        <v>48172</v>
+      </c>
+      <c r="B214" t="s">
+        <v>4</v>
+      </c>
+      <c r="C214" t="s">
+        <v>5</v>
+      </c>
+      <c r="D214" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A215">
+        <v>48192</v>
+      </c>
+      <c r="B215" t="s">
+        <v>4</v>
+      </c>
+      <c r="C215" t="s">
+        <v>5</v>
+      </c>
+      <c r="D215" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A216">
+        <v>48193</v>
+      </c>
+      <c r="B216" t="s">
+        <v>4</v>
+      </c>
+      <c r="C216" t="s">
+        <v>5</v>
+      </c>
+      <c r="D216" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A217">
+        <v>48244</v>
+      </c>
+      <c r="B217" t="s">
+        <v>4</v>
+      </c>
+      <c r="C217" t="s">
+        <v>5</v>
+      </c>
+      <c r="D217" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A218">
+        <v>48533</v>
+      </c>
+      <c r="B218" t="s">
+        <v>4</v>
+      </c>
+      <c r="C218" t="s">
+        <v>5</v>
+      </c>
+      <c r="D218" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A219">
+        <v>48634</v>
+      </c>
+      <c r="B219" t="s">
+        <v>13</v>
+      </c>
+      <c r="C219" t="s">
+        <v>14</v>
+      </c>
+      <c r="D219" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A220">
+        <v>48639</v>
+      </c>
+      <c r="B220" t="s">
+        <v>4</v>
+      </c>
+      <c r="C220" t="s">
+        <v>5</v>
+      </c>
+      <c r="D220" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A221">
+        <v>48724</v>
+      </c>
+      <c r="B221" t="s">
+        <v>4</v>
+      </c>
+      <c r="C221" t="s">
+        <v>5</v>
+      </c>
+      <c r="D221" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A222">
+        <v>48758</v>
+      </c>
+      <c r="B222" t="s">
+        <v>13</v>
+      </c>
+      <c r="C222" t="s">
+        <v>14</v>
+      </c>
+      <c r="D222" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A223">
+        <v>48761</v>
+      </c>
+      <c r="B223" t="s">
+        <v>4</v>
+      </c>
+      <c r="C223" t="s">
+        <v>5</v>
+      </c>
+      <c r="D223" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A224">
+        <v>48762</v>
+      </c>
+      <c r="B224" t="s">
+        <v>4</v>
+      </c>
+      <c r="C224" t="s">
+        <v>5</v>
+      </c>
+      <c r="D224" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A225">
+        <v>48833</v>
+      </c>
+      <c r="B225" t="s">
+        <v>4</v>
+      </c>
+      <c r="C225" t="s">
+        <v>5</v>
+      </c>
+      <c r="D225" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A226">
+        <v>48834</v>
+      </c>
+      <c r="B226" t="s">
+        <v>4</v>
+      </c>
+      <c r="C226" t="s">
+        <v>5</v>
+      </c>
+      <c r="D226" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A227">
+        <v>48853</v>
+      </c>
+      <c r="B227" t="s">
+        <v>13</v>
+      </c>
+      <c r="C227" t="s">
+        <v>14</v>
+      </c>
+      <c r="D227" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A228">
+        <v>49014</v>
+      </c>
+      <c r="B228" t="s">
+        <v>4</v>
+      </c>
+      <c r="C228" t="s">
+        <v>5</v>
+      </c>
+      <c r="D228" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A229">
+        <v>49233</v>
+      </c>
+      <c r="B229" t="s">
+        <v>4</v>
+      </c>
+      <c r="C229" t="s">
+        <v>5</v>
+      </c>
+      <c r="D229" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A230">
+        <v>49261</v>
+      </c>
+      <c r="B230" t="s">
+        <v>4</v>
+      </c>
+      <c r="C230" t="s">
+        <v>5</v>
+      </c>
+      <c r="D230" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A231">
+        <v>49353</v>
+      </c>
+      <c r="B231" t="s">
+        <v>4</v>
+      </c>
+      <c r="C231" t="s">
+        <v>5</v>
+      </c>
+      <c r="D231" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A232">
+        <v>49366</v>
+      </c>
+      <c r="B232" t="s">
+        <v>4</v>
+      </c>
+      <c r="C232" t="s">
+        <v>5</v>
+      </c>
+      <c r="D232" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A233">
+        <v>49407</v>
+      </c>
+      <c r="B233" t="s">
+        <v>13</v>
+      </c>
+      <c r="C233" t="s">
+        <v>14</v>
+      </c>
+      <c r="D233" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A234">
+        <v>49487</v>
+      </c>
+      <c r="B234" t="s">
+        <v>4</v>
+      </c>
+      <c r="C234" t="s">
+        <v>5</v>
+      </c>
+      <c r="D234" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A235">
+        <v>49488</v>
+      </c>
+      <c r="B235" t="s">
+        <v>4</v>
+      </c>
+      <c r="C235" t="s">
+        <v>5</v>
+      </c>
+      <c r="D235" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A236">
+        <v>49622</v>
+      </c>
+      <c r="B236" t="s">
+        <v>4</v>
+      </c>
+      <c r="C236" t="s">
+        <v>5</v>
+      </c>
+      <c r="D236" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A237">
+        <v>49634</v>
+      </c>
+      <c r="B237" t="s">
+        <v>13</v>
+      </c>
+      <c r="C237" t="s">
+        <v>14</v>
+      </c>
+      <c r="D237" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A238">
+        <v>49645</v>
+      </c>
+      <c r="B238" t="s">
+        <v>4</v>
+      </c>
+      <c r="C238" t="s">
+        <v>5</v>
+      </c>
+      <c r="D238" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A239">
+        <v>49700</v>
+      </c>
+      <c r="B239" t="s">
+        <v>4</v>
+      </c>
+      <c r="C239" t="s">
+        <v>5</v>
+      </c>
+      <c r="D239" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A240">
+        <v>49707</v>
+      </c>
+      <c r="B240" t="s">
+        <v>4</v>
+      </c>
+      <c r="C240" t="s">
+        <v>5</v>
+      </c>
+      <c r="D240" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A241">
+        <v>49817</v>
+      </c>
+      <c r="B241" t="s">
+        <v>4</v>
+      </c>
+      <c r="C241" t="s">
+        <v>5</v>
+      </c>
+      <c r="D241" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A242">
+        <v>50006</v>
+      </c>
+      <c r="B242" t="s">
+        <v>4</v>
+      </c>
+      <c r="C242" t="s">
+        <v>5</v>
+      </c>
+      <c r="D242" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A243">
+        <v>50147</v>
+      </c>
+      <c r="B243" t="s">
+        <v>4</v>
+      </c>
+      <c r="C243" t="s">
+        <v>5</v>
+      </c>
+      <c r="D243" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A244">
+        <v>50177</v>
+      </c>
+      <c r="B244" t="s">
+        <v>4</v>
+      </c>
+      <c r="C244" t="s">
+        <v>5</v>
+      </c>
+      <c r="D244" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A245">
+        <v>50189</v>
+      </c>
+      <c r="B245" t="s">
+        <v>4</v>
+      </c>
+      <c r="C245" t="s">
+        <v>5</v>
+      </c>
+      <c r="D245" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A246">
+        <v>50281</v>
+      </c>
+      <c r="B246" t="s">
+        <v>4</v>
+      </c>
+      <c r="C246" t="s">
+        <v>5</v>
+      </c>
+      <c r="D246" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A247">
+        <v>50282</v>
+      </c>
+      <c r="B247" t="s">
+        <v>4</v>
+      </c>
+      <c r="C247" t="s">
+        <v>5</v>
+      </c>
+      <c r="D247" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A248">
+        <v>50505</v>
+      </c>
+      <c r="B248" t="s">
+        <v>4</v>
+      </c>
+      <c r="C248" t="s">
+        <v>5</v>
+      </c>
+      <c r="D248" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A249">
+        <v>50637</v>
+      </c>
+      <c r="B249" t="s">
+        <v>4</v>
+      </c>
+      <c r="C249" t="s">
+        <v>5</v>
+      </c>
+      <c r="D249" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A250">
+        <v>50638</v>
+      </c>
+      <c r="B250" t="s">
+        <v>4</v>
+      </c>
+      <c r="C250" t="s">
+        <v>5</v>
+      </c>
+      <c r="D250" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A251">
+        <v>50639</v>
+      </c>
+      <c r="B251" t="s">
+        <v>4</v>
+      </c>
+      <c r="C251" t="s">
+        <v>5</v>
+      </c>
+      <c r="D251" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A252">
+        <v>50877</v>
+      </c>
+      <c r="B252" t="s">
+        <v>4</v>
+      </c>
+      <c r="C252" t="s">
+        <v>5</v>
+      </c>
+      <c r="D252" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A253">
+        <v>50879</v>
+      </c>
+      <c r="B253" t="s">
+        <v>4</v>
+      </c>
+      <c r="C253" t="s">
+        <v>5</v>
+      </c>
+      <c r="D253" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A254">
+        <v>50930</v>
+      </c>
+      <c r="B254" t="s">
+        <v>4</v>
+      </c>
+      <c r="C254" t="s">
+        <v>5</v>
+      </c>
+      <c r="D254" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A255">
+        <v>50931</v>
+      </c>
+      <c r="B255" t="s">
+        <v>4</v>
+      </c>
+      <c r="C255" t="s">
+        <v>5</v>
+      </c>
+      <c r="D255" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A256">
+        <v>50932</v>
+      </c>
+      <c r="B256" t="s">
+        <v>4</v>
+      </c>
+      <c r="C256" t="s">
+        <v>5</v>
+      </c>
+      <c r="D256" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A257">
+        <v>50957</v>
+      </c>
+      <c r="B257" t="s">
+        <v>4</v>
+      </c>
+      <c r="C257" t="s">
+        <v>5</v>
+      </c>
+      <c r="D257" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A258">
+        <v>51068</v>
+      </c>
+      <c r="B258" t="s">
+        <v>4</v>
+      </c>
+      <c r="C258" t="s">
+        <v>5</v>
+      </c>
+      <c r="D258" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A259">
+        <v>51146</v>
+      </c>
+      <c r="B259" t="s">
+        <v>13</v>
+      </c>
+      <c r="C259" t="s">
+        <v>14</v>
+      </c>
+      <c r="D259" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A260">
+        <v>51197</v>
+      </c>
+      <c r="B260" t="s">
+        <v>4</v>
+      </c>
+      <c r="C260" t="s">
+        <v>5</v>
+      </c>
+      <c r="D260" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A261">
+        <v>51393</v>
+      </c>
+      <c r="B261" t="s">
+        <v>4</v>
+      </c>
+      <c r="C261" t="s">
+        <v>5</v>
+      </c>
+      <c r="D261" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A262">
+        <v>51450</v>
+      </c>
+      <c r="B262" t="s">
+        <v>4</v>
+      </c>
+      <c r="C262" t="s">
+        <v>5</v>
+      </c>
+      <c r="D262" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A263">
+        <v>51451</v>
+      </c>
+      <c r="B263" t="s">
+        <v>4</v>
+      </c>
+      <c r="C263" t="s">
+        <v>5</v>
+      </c>
+      <c r="D263" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A264">
+        <v>51454</v>
+      </c>
+      <c r="B264" t="s">
+        <v>4</v>
+      </c>
+      <c r="C264" t="s">
+        <v>5</v>
+      </c>
+      <c r="D264" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A265">
+        <v>51558</v>
+      </c>
+      <c r="B265" t="s">
+        <v>13</v>
+      </c>
+      <c r="C265" t="s">
+        <v>14</v>
+      </c>
+      <c r="D265" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A266">
+        <v>51846</v>
+      </c>
+      <c r="B266" t="s">
+        <v>4</v>
+      </c>
+      <c r="C266" t="s">
+        <v>5</v>
+      </c>
+      <c r="D266" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A267">
+        <v>51847</v>
+      </c>
+      <c r="B267" t="s">
+        <v>4</v>
+      </c>
+      <c r="C267" t="s">
+        <v>5</v>
+      </c>
+      <c r="D267" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A268">
+        <v>51990</v>
+      </c>
+      <c r="B268" t="s">
+        <v>4</v>
+      </c>
+      <c r="C268" t="s">
+        <v>5</v>
+      </c>
+      <c r="D268" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A269">
+        <v>51991</v>
+      </c>
+      <c r="B269" t="s">
+        <v>13</v>
+      </c>
+      <c r="C269" t="s">
+        <v>14</v>
+      </c>
+      <c r="D269" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A270">
+        <v>52000</v>
+      </c>
+      <c r="B270" t="s">
+        <v>4</v>
+      </c>
+      <c r="C270" t="s">
+        <v>5</v>
+      </c>
+      <c r="D270" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A271">
+        <v>52001</v>
+      </c>
+      <c r="B271" t="s">
+        <v>4</v>
+      </c>
+      <c r="C271" t="s">
+        <v>5</v>
+      </c>
+      <c r="D271" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A272">
+        <v>52002</v>
+      </c>
+      <c r="B272" t="s">
+        <v>4</v>
+      </c>
+      <c r="C272" t="s">
+        <v>5</v>
+      </c>
+      <c r="D272" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A273">
+        <v>52040</v>
+      </c>
+      <c r="B273" t="s">
+        <v>13</v>
+      </c>
+      <c r="C273" t="s">
+        <v>14</v>
+      </c>
+      <c r="D273" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A274">
+        <v>52182</v>
+      </c>
+      <c r="B274" t="s">
+        <v>4</v>
+      </c>
+      <c r="C274" t="s">
+        <v>5</v>
+      </c>
+      <c r="D274" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A275">
+        <v>52187</v>
+      </c>
+      <c r="B275" t="s">
+        <v>13</v>
+      </c>
+      <c r="C275" t="s">
+        <v>14</v>
+      </c>
+      <c r="D275" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A276">
+        <v>52205</v>
+      </c>
+      <c r="B276" t="s">
+        <v>4</v>
+      </c>
+      <c r="C276" t="s">
+        <v>5</v>
+      </c>
+      <c r="D276" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A277">
+        <v>52266</v>
+      </c>
+      <c r="B277" t="s">
+        <v>4</v>
+      </c>
+      <c r="C277" t="s">
+        <v>5</v>
+      </c>
+      <c r="D277" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A278">
+        <v>52270</v>
+      </c>
+      <c r="B278" t="s">
+        <v>4</v>
+      </c>
+      <c r="C278" t="s">
+        <v>5</v>
+      </c>
+      <c r="D278" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A279">
+        <v>52317</v>
+      </c>
+      <c r="B279" t="s">
+        <v>13</v>
+      </c>
+      <c r="C279" t="s">
+        <v>14</v>
+      </c>
+      <c r="D279" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A280">
+        <v>52360</v>
+      </c>
+      <c r="B280" t="s">
+        <v>4</v>
+      </c>
+      <c r="C280" t="s">
+        <v>5</v>
+      </c>
+      <c r="D280" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A281">
+        <v>52378</v>
+      </c>
+      <c r="B281" t="s">
+        <v>4</v>
+      </c>
+      <c r="C281" t="s">
+        <v>5</v>
+      </c>
+      <c r="D281" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A282">
+        <v>52434</v>
+      </c>
+      <c r="B282" t="s">
+        <v>4</v>
+      </c>
+      <c r="C282" t="s">
+        <v>5</v>
+      </c>
+      <c r="D282" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A283">
+        <v>52463</v>
+      </c>
+      <c r="B283" t="s">
+        <v>4</v>
+      </c>
+      <c r="C283" t="s">
+        <v>5</v>
+      </c>
+      <c r="D283" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A284">
+        <v>52464</v>
+      </c>
+      <c r="B284" t="s">
+        <v>13</v>
+      </c>
+      <c r="C284" t="s">
+        <v>14</v>
+      </c>
+      <c r="D284" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A285">
+        <v>52465</v>
+      </c>
+      <c r="B285" t="s">
+        <v>13</v>
+      </c>
+      <c r="C285" t="s">
+        <v>14</v>
+      </c>
+      <c r="D285" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A286">
+        <v>52466</v>
+      </c>
+      <c r="B286" t="s">
+        <v>13</v>
+      </c>
+      <c r="C286" t="s">
+        <v>14</v>
+      </c>
+      <c r="D286" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A287">
+        <v>52467</v>
+      </c>
+      <c r="B287" t="s">
+        <v>13</v>
+      </c>
+      <c r="C287" t="s">
+        <v>14</v>
+      </c>
+      <c r="D287" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A288">
+        <v>52631</v>
+      </c>
+      <c r="B288" t="s">
+        <v>13</v>
+      </c>
+      <c r="C288" t="s">
+        <v>14</v>
+      </c>
+      <c r="D288" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A289">
+        <v>52635</v>
+      </c>
+      <c r="B289" t="s">
+        <v>13</v>
+      </c>
+      <c r="C289" t="s">
+        <v>14</v>
+      </c>
+      <c r="D289" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A290">
+        <v>52672</v>
+      </c>
+      <c r="B290" t="s">
+        <v>4</v>
+      </c>
+      <c r="C290" t="s">
+        <v>5</v>
+      </c>
+      <c r="D290" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A291">
+        <v>52673</v>
+      </c>
+      <c r="B291" t="s">
+        <v>4</v>
+      </c>
+      <c r="C291" t="s">
+        <v>5</v>
+      </c>
+      <c r="D291" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A292">
+        <v>52725</v>
+      </c>
+      <c r="B292" t="s">
+        <v>4</v>
+      </c>
+      <c r="C292" t="s">
+        <v>5</v>
+      </c>
+      <c r="D292" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A293">
+        <v>52730</v>
+      </c>
+      <c r="B293" t="s">
+        <v>4</v>
+      </c>
+      <c r="C293" t="s">
+        <v>5</v>
+      </c>
+      <c r="D293" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A294">
+        <v>52923</v>
+      </c>
+      <c r="B294" t="s">
+        <v>13</v>
+      </c>
+      <c r="C294" t="s">
+        <v>14</v>
+      </c>
+      <c r="D294" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A295">
+        <v>52947</v>
+      </c>
+      <c r="B295" t="s">
+        <v>4</v>
+      </c>
+      <c r="C295" t="s">
+        <v>5</v>
+      </c>
+      <c r="D295" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A296">
+        <v>53212</v>
+      </c>
+      <c r="B296" t="s">
+        <v>4</v>
+      </c>
+      <c r="C296" t="s">
+        <v>5</v>
+      </c>
+      <c r="D296" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A297">
+        <v>53273</v>
+      </c>
+      <c r="B297" t="s">
+        <v>4</v>
+      </c>
+      <c r="C297" t="s">
+        <v>5</v>
+      </c>
+      <c r="D297" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A298">
+        <v>53487</v>
+      </c>
+      <c r="B298" t="s">
+        <v>4</v>
+      </c>
+      <c r="C298" t="s">
+        <v>5</v>
+      </c>
+      <c r="D298" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A299">
+        <v>53488</v>
+      </c>
+      <c r="B299" t="s">
+        <v>13</v>
+      </c>
+      <c r="C299" t="s">
+        <v>14</v>
+      </c>
+      <c r="D299" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A300">
+        <v>53558</v>
+      </c>
+      <c r="B300" t="s">
+        <v>4</v>
+      </c>
+      <c r="C300" t="s">
+        <v>5</v>
+      </c>
+      <c r="D300" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A301">
+        <v>53672</v>
+      </c>
+      <c r="B301" t="s">
+        <v>4</v>
+      </c>
+      <c r="C301" t="s">
+        <v>5</v>
+      </c>
+      <c r="D301" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A302">
+        <v>53842</v>
+      </c>
+      <c r="B302" t="s">
+        <v>4</v>
+      </c>
+      <c r="C302" t="s">
+        <v>5</v>
+      </c>
+      <c r="D302" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A303">
+        <v>53850</v>
+      </c>
+      <c r="B303" t="s">
+        <v>4</v>
+      </c>
+      <c r="C303" t="s">
+        <v>5</v>
+      </c>
+      <c r="D303" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A304">
+        <v>53968</v>
+      </c>
+      <c r="B304" t="s">
+        <v>4</v>
+      </c>
+      <c r="C304" t="s">
+        <v>5</v>
+      </c>
+      <c r="D304" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A305">
+        <v>53969</v>
+      </c>
+      <c r="B305" t="s">
+        <v>4</v>
+      </c>
+      <c r="C305" t="s">
+        <v>5</v>
+      </c>
+      <c r="D305" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A306">
+        <v>54159</v>
+      </c>
+      <c r="B306" t="s">
+        <v>4</v>
+      </c>
+      <c r="C306" t="s">
+        <v>5</v>
+      </c>
+      <c r="D306" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A307">
+        <v>54160</v>
+      </c>
+      <c r="B307" t="s">
+        <v>4</v>
+      </c>
+      <c r="C307" t="s">
+        <v>5</v>
+      </c>
+      <c r="D307" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A308">
+        <v>54163</v>
+      </c>
+      <c r="B308" t="s">
+        <v>4</v>
+      </c>
+      <c r="C308" t="s">
+        <v>5</v>
+      </c>
+      <c r="D308" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A309">
+        <v>54303</v>
+      </c>
+      <c r="B309" t="s">
+        <v>4</v>
+      </c>
+      <c r="C309" t="s">
+        <v>5</v>
+      </c>
+      <c r="D309" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A310">
+        <v>54304</v>
+      </c>
+      <c r="B310" t="s">
+        <v>4</v>
+      </c>
+      <c r="C310" t="s">
+        <v>5</v>
+      </c>
+      <c r="D310" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A311">
+        <v>54454</v>
+      </c>
+      <c r="B311" t="s">
+        <v>4</v>
+      </c>
+      <c r="C311" t="s">
+        <v>5</v>
+      </c>
+      <c r="D311" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A312">
+        <v>54455</v>
+      </c>
+      <c r="B312" t="s">
+        <v>4</v>
+      </c>
+      <c r="C312" t="s">
+        <v>5</v>
+      </c>
+      <c r="D312" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A313">
+        <v>54554</v>
+      </c>
+      <c r="B313" t="s">
+        <v>4</v>
+      </c>
+      <c r="C313" t="s">
+        <v>5</v>
+      </c>
+      <c r="D313" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A314">
+        <v>54555</v>
+      </c>
+      <c r="B314" t="s">
+        <v>4</v>
+      </c>
+      <c r="C314" t="s">
+        <v>5</v>
+      </c>
+      <c r="D314" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A315">
+        <v>54556</v>
+      </c>
+      <c r="B315" t="s">
+        <v>4</v>
+      </c>
+      <c r="C315" t="s">
+        <v>5</v>
+      </c>
+      <c r="D315" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A316">
+        <v>54557</v>
+      </c>
+      <c r="B316" t="s">
+        <v>4</v>
+      </c>
+      <c r="C316" t="s">
+        <v>5</v>
+      </c>
+      <c r="D316" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A317">
+        <v>54558</v>
+      </c>
+      <c r="B317" t="s">
+        <v>4</v>
+      </c>
+      <c r="C317" t="s">
+        <v>5</v>
+      </c>
+      <c r="D317" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A318">
+        <v>54596</v>
+      </c>
+      <c r="B318" t="s">
+        <v>13</v>
+      </c>
+      <c r="C318" t="s">
+        <v>14</v>
+      </c>
+      <c r="D318" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A319">
+        <v>54845</v>
+      </c>
+      <c r="B319" t="s">
+        <v>4</v>
+      </c>
+      <c r="C319" t="s">
+        <v>5</v>
+      </c>
+      <c r="D319" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A320">
+        <v>54964</v>
+      </c>
+      <c r="B320" t="s">
+        <v>4</v>
+      </c>
+      <c r="C320" t="s">
+        <v>5</v>
+      </c>
+      <c r="D320" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A321">
+        <v>55299</v>
+      </c>
+      <c r="B321" t="s">
+        <v>13</v>
+      </c>
+      <c r="C321" t="s">
+        <v>14</v>
+      </c>
+      <c r="D321" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A322">
+        <v>55300</v>
+      </c>
+      <c r="B322" t="s">
+        <v>4</v>
+      </c>
+      <c r="C322" t="s">
+        <v>5</v>
+      </c>
+      <c r="D322" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A323">
+        <v>55391</v>
+      </c>
+      <c r="B323" t="s">
+        <v>4</v>
+      </c>
+      <c r="C323" t="s">
+        <v>5</v>
+      </c>
+      <c r="D323" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A324">
+        <v>55392</v>
+      </c>
+      <c r="B324" t="s">
+        <v>4</v>
+      </c>
+      <c r="C324" t="s">
+        <v>5</v>
+      </c>
+      <c r="D324" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A325">
+        <v>55394</v>
+      </c>
+      <c r="B325" t="s">
+        <v>4</v>
+      </c>
+      <c r="C325" t="s">
+        <v>5</v>
+      </c>
+      <c r="D325" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A326">
+        <v>55513</v>
+      </c>
+      <c r="B326" t="s">
+        <v>4</v>
+      </c>
+      <c r="C326" t="s">
+        <v>5</v>
+      </c>
+      <c r="D326" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A327">
+        <v>55889</v>
+      </c>
+      <c r="B327" t="s">
+        <v>4</v>
+      </c>
+      <c r="C327" t="s">
+        <v>5</v>
+      </c>
+      <c r="D327" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A328">
+        <v>55890</v>
+      </c>
+      <c r="B328" t="s">
+        <v>4</v>
+      </c>
+      <c r="C328" t="s">
+        <v>5</v>
+      </c>
+      <c r="D328" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A329">
+        <v>56063</v>
+      </c>
+      <c r="B329" t="s">
+        <v>4</v>
+      </c>
+      <c r="C329" t="s">
+        <v>5</v>
+      </c>
+      <c r="D329" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A330">
+        <v>56064</v>
+      </c>
+      <c r="B330" t="s">
+        <v>4</v>
+      </c>
+      <c r="C330" t="s">
+        <v>5</v>
+      </c>
+      <c r="D330" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A331">
+        <v>56065</v>
+      </c>
+      <c r="B331" t="s">
+        <v>4</v>
+      </c>
+      <c r="C331" t="s">
+        <v>5</v>
+      </c>
+      <c r="D331" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A332">
+        <v>56209</v>
+      </c>
+      <c r="B332" t="s">
+        <v>13</v>
+      </c>
+      <c r="C332" t="s">
+        <v>14</v>
+      </c>
+      <c r="D332" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A333">
+        <v>56210</v>
+      </c>
+      <c r="B333" t="s">
+        <v>13</v>
+      </c>
+      <c r="C333" t="s">
+        <v>14</v>
+      </c>
+      <c r="D333" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A334">
+        <v>56211</v>
+      </c>
+      <c r="B334" t="s">
+        <v>13</v>
+      </c>
+      <c r="C334" t="s">
+        <v>14</v>
+      </c>
+      <c r="D334" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A335">
+        <v>56216</v>
+      </c>
+      <c r="B335" t="s">
+        <v>4</v>
+      </c>
+      <c r="C335" t="s">
+        <v>5</v>
+      </c>
+      <c r="D335" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A336">
+        <v>56220</v>
+      </c>
+      <c r="B336" t="s">
+        <v>13</v>
+      </c>
+      <c r="C336" t="s">
+        <v>14</v>
+      </c>
+      <c r="D336" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A337">
+        <v>56221</v>
+      </c>
+      <c r="B337" t="s">
+        <v>13</v>
+      </c>
+      <c r="C337" t="s">
+        <v>14</v>
+      </c>
+      <c r="D337" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A338">
+        <v>56222</v>
+      </c>
+      <c r="B338" t="s">
+        <v>4</v>
+      </c>
+      <c r="C338" t="s">
+        <v>5</v>
+      </c>
+      <c r="D338" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A339">
+        <v>56356</v>
+      </c>
+      <c r="B339" t="s">
+        <v>4</v>
+      </c>
+      <c r="C339" t="s">
+        <v>5</v>
+      </c>
+      <c r="D339" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A340">
+        <v>56366</v>
+      </c>
+      <c r="B340" t="s">
+        <v>4</v>
+      </c>
+      <c r="C340" t="s">
+        <v>5</v>
+      </c>
+      <c r="D340" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A341">
+        <v>56367</v>
+      </c>
+      <c r="B341" t="s">
+        <v>4</v>
+      </c>
+      <c r="C341" t="s">
+        <v>5</v>
+      </c>
+      <c r="D341" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A342">
+        <v>56372</v>
+      </c>
+      <c r="B342" t="s">
+        <v>4</v>
+      </c>
+      <c r="C342" t="s">
+        <v>5</v>
+      </c>
+      <c r="D342" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A343">
+        <v>56447</v>
+      </c>
+      <c r="B343" t="s">
+        <v>4</v>
+      </c>
+      <c r="C343" t="s">
+        <v>5</v>
+      </c>
+      <c r="D343" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A344">
+        <v>56450</v>
+      </c>
+      <c r="B344" t="s">
+        <v>13</v>
+      </c>
+      <c r="C344" t="s">
+        <v>14</v>
+      </c>
+      <c r="D344" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A345">
+        <v>56451</v>
+      </c>
+      <c r="B345" t="s">
+        <v>13</v>
+      </c>
+      <c r="C345" t="s">
+        <v>14</v>
+      </c>
+      <c r="D345" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A346">
+        <v>56517</v>
+      </c>
+      <c r="B346" t="s">
+        <v>4</v>
+      </c>
+      <c r="C346" t="s">
+        <v>5</v>
+      </c>
+      <c r="D346" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A347">
+        <v>56551</v>
+      </c>
+      <c r="B347" t="s">
+        <v>13</v>
+      </c>
+      <c r="C347" t="s">
+        <v>14</v>
+      </c>
+      <c r="D347" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A348">
+        <v>56552</v>
+      </c>
+      <c r="B348" t="s">
+        <v>13</v>
+      </c>
+      <c r="C348" t="s">
+        <v>14</v>
+      </c>
+      <c r="D348" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A349">
+        <v>56553</v>
+      </c>
+      <c r="B349" t="s">
+        <v>13</v>
+      </c>
+      <c r="C349" t="s">
+        <v>14</v>
+      </c>
+      <c r="D349" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A350">
+        <v>56554</v>
+      </c>
+      <c r="B350" t="s">
+        <v>13</v>
+      </c>
+      <c r="C350" t="s">
+        <v>14</v>
+      </c>
+      <c r="D350" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A351">
+        <v>56555</v>
+      </c>
+      <c r="B351" t="s">
+        <v>4</v>
+      </c>
+      <c r="C351" t="s">
+        <v>5</v>
+      </c>
+      <c r="D351" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A352">
+        <v>56683</v>
+      </c>
+      <c r="B352" t="s">
+        <v>4</v>
+      </c>
+      <c r="C352" t="s">
+        <v>5</v>
+      </c>
+      <c r="D352" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A353">
+        <v>56684</v>
+      </c>
+      <c r="B353" t="s">
+        <v>4</v>
+      </c>
+      <c r="C353" t="s">
+        <v>5</v>
+      </c>
+      <c r="D353" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A354">
+        <v>56705</v>
+      </c>
+      <c r="B354" t="s">
+        <v>13</v>
+      </c>
+      <c r="C354" t="s">
+        <v>14</v>
+      </c>
+      <c r="D354" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A355">
+        <v>56714</v>
+      </c>
+      <c r="B355" t="s">
+        <v>4</v>
+      </c>
+      <c r="C355" t="s">
+        <v>5</v>
+      </c>
+      <c r="D355" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A356">
+        <v>56715</v>
+      </c>
+      <c r="B356" t="s">
+        <v>4</v>
+      </c>
+      <c r="C356" t="s">
+        <v>5</v>
+      </c>
+      <c r="D356" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A357">
+        <v>56722</v>
+      </c>
+      <c r="B357" t="s">
+        <v>4</v>
+      </c>
+      <c r="C357" t="s">
+        <v>5</v>
+      </c>
+      <c r="D357" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A358">
+        <v>56723</v>
+      </c>
+      <c r="B358" t="s">
+        <v>4</v>
+      </c>
+      <c r="C358" t="s">
+        <v>5</v>
+      </c>
+      <c r="D358" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A359">
+        <v>56739</v>
+      </c>
+      <c r="B359" t="s">
+        <v>4</v>
+      </c>
+      <c r="C359" t="s">
+        <v>5</v>
+      </c>
+      <c r="D359" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A360">
+        <v>56740</v>
+      </c>
+      <c r="B360" t="s">
+        <v>4</v>
+      </c>
+      <c r="C360" t="s">
+        <v>5</v>
+      </c>
+      <c r="D360" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A361">
+        <v>56765</v>
+      </c>
+      <c r="B361" t="s">
+        <v>4</v>
+      </c>
+      <c r="C361" t="s">
+        <v>5</v>
+      </c>
+      <c r="D361" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A362">
+        <v>56842</v>
+      </c>
+      <c r="B362" t="s">
+        <v>4</v>
+      </c>
+      <c r="C362" t="s">
+        <v>5</v>
+      </c>
+      <c r="D362" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A363">
+        <v>56855</v>
+      </c>
+      <c r="B363" t="s">
+        <v>4</v>
+      </c>
+      <c r="C363" t="s">
+        <v>5</v>
+      </c>
+      <c r="D363" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A364">
+        <v>56856</v>
+      </c>
+      <c r="B364" t="s">
+        <v>4</v>
+      </c>
+      <c r="C364" t="s">
+        <v>5</v>
+      </c>
+      <c r="D364" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A365">
+        <v>57031</v>
+      </c>
+      <c r="B365" t="s">
+        <v>13</v>
+      </c>
+      <c r="C365" t="s">
+        <v>14</v>
+      </c>
+      <c r="D365" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A366">
+        <v>57042</v>
+      </c>
+      <c r="B366" t="s">
+        <v>4</v>
+      </c>
+      <c r="C366" t="s">
+        <v>5</v>
+      </c>
+      <c r="D366" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A367">
+        <v>57069</v>
+      </c>
+      <c r="B367" t="s">
+        <v>4</v>
+      </c>
+      <c r="C367" t="s">
+        <v>5</v>
+      </c>
+      <c r="D367" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A368">
+        <v>57370</v>
+      </c>
+      <c r="B368" t="s">
+        <v>4</v>
+      </c>
+      <c r="C368" t="s">
+        <v>5</v>
+      </c>
+      <c r="D368" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A369">
+        <v>57383</v>
+      </c>
+      <c r="B369" t="s">
+        <v>4</v>
+      </c>
+      <c r="C369" t="s">
+        <v>5</v>
+      </c>
+      <c r="D369" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A370">
+        <v>57471</v>
+      </c>
+      <c r="B370" t="s">
+        <v>13</v>
+      </c>
+      <c r="C370" t="s">
+        <v>14</v>
+      </c>
+      <c r="D370" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A371">
+        <v>57622</v>
+      </c>
+      <c r="B371" t="s">
+        <v>4</v>
+      </c>
+      <c r="C371" t="s">
+        <v>5</v>
+      </c>
+      <c r="D371" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A372">
+        <v>57642</v>
+      </c>
+      <c r="B372" t="s">
+        <v>4</v>
+      </c>
+      <c r="C372" t="s">
+        <v>5</v>
+      </c>
+      <c r="D372" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A373">
+        <v>57643</v>
+      </c>
+      <c r="B373" t="s">
+        <v>4</v>
+      </c>
+      <c r="C373" t="s">
+        <v>5</v>
+      </c>
+      <c r="D373" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A374">
+        <v>57644</v>
+      </c>
+      <c r="B374" t="s">
+        <v>4</v>
+      </c>
+      <c r="C374" t="s">
+        <v>5</v>
+      </c>
+      <c r="D374" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A375">
+        <v>57656</v>
+      </c>
+      <c r="B375" t="s">
+        <v>13</v>
+      </c>
+      <c r="C375" t="s">
+        <v>14</v>
+      </c>
+      <c r="D375" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A376">
+        <v>57775</v>
+      </c>
+      <c r="B376" t="s">
+        <v>4</v>
+      </c>
+      <c r="C376" t="s">
+        <v>5</v>
+      </c>
+      <c r="D376" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A377">
+        <v>57778</v>
+      </c>
+      <c r="B377" t="s">
+        <v>4</v>
+      </c>
+      <c r="C377" t="s">
+        <v>5</v>
+      </c>
+      <c r="D377" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A378">
+        <v>57784</v>
+      </c>
+      <c r="B378" t="s">
+        <v>4</v>
+      </c>
+      <c r="C378" t="s">
+        <v>5</v>
+      </c>
+      <c r="D378" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A379">
+        <v>57785</v>
+      </c>
+      <c r="B379" t="s">
+        <v>4</v>
+      </c>
+      <c r="C379" t="s">
+        <v>5</v>
+      </c>
+      <c r="D379" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A380">
+        <v>57788</v>
+      </c>
+      <c r="B380" t="s">
+        <v>4</v>
+      </c>
+      <c r="C380" t="s">
+        <v>5</v>
+      </c>
+      <c r="D380" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A381">
+        <v>57859</v>
+      </c>
+      <c r="B381" t="s">
+        <v>13</v>
+      </c>
+      <c r="C381" t="s">
+        <v>14</v>
+      </c>
+      <c r="D381" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A382">
+        <v>57860</v>
+      </c>
+      <c r="B382" t="s">
+        <v>13</v>
+      </c>
+      <c r="C382" t="s">
+        <v>14</v>
+      </c>
+      <c r="D382" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A383">
+        <v>58054</v>
+      </c>
+      <c r="B383" t="s">
+        <v>4</v>
+      </c>
+      <c r="C383" t="s">
+        <v>5</v>
+      </c>
+      <c r="D383" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A384">
+        <v>58232</v>
+      </c>
+      <c r="B384" t="s">
+        <v>4</v>
+      </c>
+      <c r="C384" t="s">
+        <v>5</v>
+      </c>
+      <c r="D384" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A385">
+        <v>58234</v>
+      </c>
+      <c r="B385" t="s">
+        <v>4</v>
+      </c>
+      <c r="C385" t="s">
+        <v>5</v>
+      </c>
+      <c r="D385" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A386">
+        <v>58262</v>
+      </c>
+      <c r="B386" t="s">
+        <v>13</v>
+      </c>
+      <c r="C386" t="s">
+        <v>14</v>
+      </c>
+      <c r="D386" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A387">
+        <v>58263</v>
+      </c>
+      <c r="B387" t="s">
+        <v>13</v>
+      </c>
+      <c r="C387" t="s">
+        <v>14</v>
+      </c>
+      <c r="D387" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A388">
+        <v>58316</v>
+      </c>
+      <c r="B388" t="s">
+        <v>4</v>
+      </c>
+      <c r="C388" t="s">
+        <v>5</v>
+      </c>
+      <c r="D388" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A389">
+        <v>58317</v>
+      </c>
+      <c r="B389" t="s">
+        <v>4</v>
+      </c>
+      <c r="C389" t="s">
+        <v>5</v>
+      </c>
+      <c r="D389" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A390">
+        <v>58318</v>
+      </c>
+      <c r="B390" t="s">
+        <v>4</v>
+      </c>
+      <c r="C390" t="s">
+        <v>5</v>
+      </c>
+      <c r="D390" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A391">
+        <v>58384</v>
+      </c>
+      <c r="B391" t="s">
+        <v>4</v>
+      </c>
+      <c r="C391" t="s">
+        <v>5</v>
+      </c>
+      <c r="D391" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="392" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A392">
+        <v>58385</v>
+      </c>
+      <c r="B392" t="s">
+        <v>4</v>
+      </c>
+      <c r="C392" t="s">
+        <v>5</v>
+      </c>
+      <c r="D392" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A393">
+        <v>58424</v>
+      </c>
+      <c r="B393" t="s">
+        <v>4</v>
+      </c>
+      <c r="C393" t="s">
+        <v>5</v>
+      </c>
+      <c r="D393" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A394">
+        <v>58601</v>
+      </c>
+      <c r="B394" t="s">
+        <v>4</v>
+      </c>
+      <c r="C394" t="s">
+        <v>5</v>
+      </c>
+      <c r="D394" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A395">
+        <v>58602</v>
+      </c>
+      <c r="B395" t="s">
+        <v>4</v>
+      </c>
+      <c r="C395" t="s">
+        <v>5</v>
+      </c>
+      <c r="D395" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A396">
+        <v>58603</v>
+      </c>
+      <c r="B396" t="s">
+        <v>4</v>
+      </c>
+      <c r="C396" t="s">
+        <v>5</v>
+      </c>
+      <c r="D396" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A397">
+        <v>58604</v>
+      </c>
+      <c r="B397" t="s">
+        <v>4</v>
+      </c>
+      <c r="C397" t="s">
+        <v>5</v>
+      </c>
+      <c r="D397" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A398">
+        <v>58605</v>
+      </c>
+      <c r="B398" t="s">
+        <v>4</v>
+      </c>
+      <c r="C398" t="s">
+        <v>5</v>
+      </c>
+      <c r="D398" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A399">
+        <v>58606</v>
+      </c>
+      <c r="B399" t="s">
+        <v>4</v>
+      </c>
+      <c r="C399" t="s">
+        <v>5</v>
+      </c>
+      <c r="D399" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A400">
+        <v>58607</v>
+      </c>
+      <c r="B400" t="s">
+        <v>4</v>
+      </c>
+      <c r="C400" t="s">
+        <v>5</v>
+      </c>
+      <c r="D400" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A401">
+        <v>58608</v>
+      </c>
+      <c r="B401" t="s">
+        <v>13</v>
+      </c>
+      <c r="C401" t="s">
+        <v>14</v>
+      </c>
+      <c r="D401" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A402">
+        <v>58610</v>
+      </c>
+      <c r="B402" t="s">
+        <v>4</v>
+      </c>
+      <c r="C402" t="s">
+        <v>5</v>
+      </c>
+      <c r="D402" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A403">
+        <v>58611</v>
+      </c>
+      <c r="B403" t="s">
+        <v>4</v>
+      </c>
+      <c r="C403" t="s">
+        <v>5</v>
+      </c>
+      <c r="D403" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A404">
+        <v>58612</v>
+      </c>
+      <c r="B404" t="s">
+        <v>4</v>
+      </c>
+      <c r="C404" t="s">
+        <v>5</v>
+      </c>
+      <c r="D404" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A405">
+        <v>58613</v>
+      </c>
+      <c r="B405" t="s">
+        <v>4</v>
+      </c>
+      <c r="C405" t="s">
+        <v>5</v>
+      </c>
+      <c r="D405" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A406">
+        <v>58614</v>
+      </c>
+      <c r="B406" t="s">
+        <v>13</v>
+      </c>
+      <c r="C406" t="s">
+        <v>14</v>
+      </c>
+      <c r="D406" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A407">
+        <v>58615</v>
+      </c>
+      <c r="B407" t="s">
+        <v>4</v>
+      </c>
+      <c r="C407" t="s">
+        <v>5</v>
+      </c>
+      <c r="D407" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A408">
+        <v>58617</v>
+      </c>
+      <c r="B408" t="s">
+        <v>4</v>
+      </c>
+      <c r="C408" t="s">
+        <v>5</v>
+      </c>
+      <c r="D408" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A409">
+        <v>58618</v>
+      </c>
+      <c r="B409" t="s">
+        <v>4</v>
+      </c>
+      <c r="C409" t="s">
+        <v>5</v>
+      </c>
+      <c r="D409" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="410" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A410">
+        <v>58619</v>
+      </c>
+      <c r="B410" t="s">
+        <v>4</v>
+      </c>
+      <c r="C410" t="s">
+        <v>5</v>
+      </c>
+      <c r="D410" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A411">
+        <v>58626</v>
+      </c>
+      <c r="B411" t="s">
+        <v>13</v>
+      </c>
+      <c r="C411" t="s">
+        <v>14</v>
+      </c>
+      <c r="D411" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="412" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A412">
+        <v>58778</v>
+      </c>
+      <c r="B412" t="s">
+        <v>4</v>
+      </c>
+      <c r="C412" t="s">
+        <v>5</v>
+      </c>
+      <c r="D412" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="413" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A413">
+        <v>58779</v>
+      </c>
+      <c r="B413" t="s">
+        <v>4</v>
+      </c>
+      <c r="C413" t="s">
+        <v>5</v>
+      </c>
+      <c r="D413" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="414" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A414">
+        <v>58902</v>
+      </c>
+      <c r="B414" t="s">
+        <v>13</v>
+      </c>
+      <c r="C414" t="s">
+        <v>14</v>
+      </c>
+      <c r="D414" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A415">
+        <v>59141</v>
+      </c>
+      <c r="B415" t="s">
+        <v>4</v>
+      </c>
+      <c r="C415" t="s">
+        <v>5</v>
+      </c>
+      <c r="D415" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A416">
+        <v>59206</v>
+      </c>
+      <c r="B416" t="s">
+        <v>4</v>
+      </c>
+      <c r="C416" t="s">
+        <v>5</v>
+      </c>
+      <c r="D416" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="417" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A417">
+        <v>59371</v>
+      </c>
+      <c r="B417" t="s">
+        <v>13</v>
+      </c>
+      <c r="C417" t="s">
+        <v>14</v>
+      </c>
+      <c r="D417" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="418" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A418">
+        <v>59372</v>
+      </c>
+      <c r="B418" t="s">
+        <v>13</v>
+      </c>
+      <c r="C418" t="s">
+        <v>14</v>
+      </c>
+      <c r="D418" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="419" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A419">
+        <v>59551</v>
+      </c>
+      <c r="B419" t="s">
+        <v>13</v>
+      </c>
+      <c r="C419" t="s">
+        <v>14</v>
+      </c>
+      <c r="D419" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="420" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A420">
+        <v>59552</v>
+      </c>
+      <c r="B420" t="s">
+        <v>13</v>
+      </c>
+      <c r="C420" t="s">
+        <v>14</v>
+      </c>
+      <c r="D420" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="421" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A421">
+        <v>60131</v>
+      </c>
+      <c r="B421" t="s">
+        <v>4</v>
+      </c>
+      <c r="C421" t="s">
+        <v>5</v>
+      </c>
+      <c r="D421" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="422" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A422">
+        <v>60132</v>
+      </c>
+      <c r="B422" t="s">
+        <v>4</v>
+      </c>
+      <c r="C422" t="s">
+        <v>5</v>
+      </c>
+      <c r="D422" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="423" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A423">
+        <v>60133</v>
+      </c>
+      <c r="B423" t="s">
+        <v>4</v>
+      </c>
+      <c r="C423" t="s">
+        <v>5</v>
+      </c>
+      <c r="D423" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="424" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A424">
+        <v>60185</v>
+      </c>
+      <c r="B424" t="s">
+        <v>4</v>
+      </c>
+      <c r="C424" t="s">
+        <v>5</v>
+      </c>
+      <c r="D424" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="425" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A425">
+        <v>60246</v>
+      </c>
+      <c r="B425" t="s">
+        <v>4</v>
+      </c>
+      <c r="C425" t="s">
+        <v>5</v>
+      </c>
+      <c r="D425" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="426" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A426">
+        <v>60247</v>
+      </c>
+      <c r="B426" t="s">
+        <v>4</v>
+      </c>
+      <c r="C426" t="s">
+        <v>5</v>
+      </c>
+      <c r="D426" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="427" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A427">
+        <v>60294</v>
+      </c>
+      <c r="B427" t="s">
+        <v>4</v>
+      </c>
+      <c r="C427" t="s">
+        <v>5</v>
+      </c>
+      <c r="D427" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="428" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A428">
+        <v>60327</v>
+      </c>
+      <c r="B428" t="s">
+        <v>4</v>
+      </c>
+      <c r="C428" t="s">
+        <v>5</v>
+      </c>
+      <c r="D428" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="429" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A429">
+        <v>60330</v>
+      </c>
+      <c r="B429" t="s">
+        <v>4</v>
+      </c>
+      <c r="C429" t="s">
+        <v>5</v>
+      </c>
+      <c r="D429" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="430" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A430">
+        <v>60345</v>
+      </c>
+      <c r="B430" t="s">
+        <v>4</v>
+      </c>
+      <c r="C430" t="s">
+        <v>5</v>
+      </c>
+      <c r="D430" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="431" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A431">
+        <v>60374</v>
+      </c>
+      <c r="B431" t="s">
+        <v>4</v>
+      </c>
+      <c r="C431" t="s">
+        <v>5</v>
+      </c>
+      <c r="D431" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="432" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A432">
+        <v>60515</v>
+      </c>
+      <c r="B432" t="s">
+        <v>4</v>
+      </c>
+      <c r="C432" t="s">
+        <v>5</v>
+      </c>
+      <c r="D432" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="433" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A433">
+        <v>60648</v>
+      </c>
+      <c r="B433" t="s">
+        <v>4</v>
+      </c>
+      <c r="C433" t="s">
+        <v>5</v>
+      </c>
+      <c r="D433" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="434" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A434">
+        <v>60649</v>
+      </c>
+      <c r="B434" t="s">
+        <v>4</v>
+      </c>
+      <c r="C434" t="s">
+        <v>5</v>
+      </c>
+      <c r="D434" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="435" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A435">
+        <v>60665</v>
+      </c>
+      <c r="B435" t="s">
+        <v>4</v>
+      </c>
+      <c r="C435" t="s">
+        <v>5</v>
+      </c>
+      <c r="D435" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="436" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A436">
+        <v>60703</v>
+      </c>
+      <c r="B436" t="s">
+        <v>13</v>
+      </c>
+      <c r="C436" t="s">
+        <v>14</v>
+      </c>
+      <c r="D436" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="437" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A437">
+        <v>60705</v>
+      </c>
+      <c r="B437" t="s">
+        <v>4</v>
+      </c>
+      <c r="C437" t="s">
+        <v>5</v>
+      </c>
+      <c r="D437" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="438" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A438">
+        <v>60759</v>
+      </c>
+      <c r="B438" t="s">
+        <v>4</v>
+      </c>
+      <c r="C438" t="s">
+        <v>5</v>
+      </c>
+      <c r="D438" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="439" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A439">
+        <v>60760</v>
+      </c>
+      <c r="B439" t="s">
+        <v>4</v>
+      </c>
+      <c r="C439" t="s">
+        <v>5</v>
+      </c>
+      <c r="D439" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="440" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A440">
+        <v>60809</v>
+      </c>
+      <c r="B440" t="s">
+        <v>4</v>
+      </c>
+      <c r="C440" t="s">
+        <v>5</v>
+      </c>
+      <c r="D440" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="441" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A441">
+        <v>60810</v>
+      </c>
+      <c r="B441" t="s">
+        <v>4</v>
+      </c>
+      <c r="C441" t="s">
+        <v>5</v>
+      </c>
+      <c r="D441" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="442" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A442">
+        <v>60851</v>
+      </c>
+      <c r="B442" t="s">
+        <v>4</v>
+      </c>
+      <c r="C442" t="s">
+        <v>5</v>
+      </c>
+      <c r="D442" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="443" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A443">
+        <v>60852</v>
+      </c>
+      <c r="B443" t="s">
+        <v>4</v>
+      </c>
+      <c r="C443" t="s">
+        <v>5</v>
+      </c>
+      <c r="D443" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="444" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A444">
+        <v>61000</v>
+      </c>
+      <c r="B444" t="s">
+        <v>4</v>
+      </c>
+      <c r="C444" t="s">
+        <v>5</v>
+      </c>
+      <c r="D444" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="445" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A445">
+        <v>61124</v>
+      </c>
+      <c r="B445" t="s">
+        <v>4</v>
+      </c>
+      <c r="C445" t="s">
+        <v>5</v>
+      </c>
+      <c r="D445" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="446" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A446">
+        <v>61215</v>
+      </c>
+      <c r="B446" t="s">
+        <v>4</v>
+      </c>
+      <c r="C446" t="s">
+        <v>5</v>
+      </c>
+      <c r="D446" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="447" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A447">
+        <v>61216</v>
+      </c>
+      <c r="B447" t="s">
+        <v>4</v>
+      </c>
+      <c r="C447" t="s">
+        <v>5</v>
+      </c>
+      <c r="D447" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="448" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A448">
+        <v>61217</v>
+      </c>
+      <c r="B448" t="s">
+        <v>4</v>
+      </c>
+      <c r="C448" t="s">
+        <v>5</v>
+      </c>
+      <c r="D448" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="449" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A449">
+        <v>61231</v>
+      </c>
+      <c r="B449" t="s">
+        <v>13</v>
+      </c>
+      <c r="C449" t="s">
+        <v>14</v>
+      </c>
+      <c r="D449" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="450" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A450">
+        <v>61253</v>
+      </c>
+      <c r="B450" t="s">
+        <v>4</v>
+      </c>
+      <c r="C450" t="s">
+        <v>5</v>
+      </c>
+      <c r="D450" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="451" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A451">
+        <v>61261</v>
+      </c>
+      <c r="B451" t="s">
+        <v>4</v>
+      </c>
+      <c r="C451" t="s">
+        <v>5</v>
+      </c>
+      <c r="D451" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="452" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A452">
+        <v>61383</v>
+      </c>
+      <c r="B452" t="s">
+        <v>4</v>
+      </c>
+      <c r="C452" t="s">
+        <v>5</v>
+      </c>
+      <c r="D452" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="453" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A453">
+        <v>61387</v>
+      </c>
+      <c r="B453" t="s">
+        <v>13</v>
+      </c>
+      <c r="C453" t="s">
+        <v>14</v>
+      </c>
+      <c r="D453" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="454" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A454">
+        <v>61470</v>
+      </c>
+      <c r="B454" t="s">
+        <v>13</v>
+      </c>
+      <c r="C454" t="s">
+        <v>14</v>
+      </c>
+      <c r="D454" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="455" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A455">
+        <v>61471</v>
+      </c>
+      <c r="B455" t="s">
+        <v>13</v>
+      </c>
+      <c r="C455" t="s">
+        <v>14</v>
+      </c>
+      <c r="D455" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="456" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A456">
+        <v>61472</v>
+      </c>
+      <c r="B456" t="s">
+        <v>13</v>
+      </c>
+      <c r="C456" t="s">
+        <v>14</v>
+      </c>
+      <c r="D456" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="457" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A457">
+        <v>61473</v>
+      </c>
+      <c r="B457" t="s">
+        <v>13</v>
+      </c>
+      <c r="C457" t="s">
+        <v>14</v>
+      </c>
+      <c r="D457" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="458" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A458">
+        <v>61474</v>
+      </c>
+      <c r="B458" t="s">
+        <v>13</v>
+      </c>
+      <c r="C458" t="s">
+        <v>14</v>
+      </c>
+      <c r="D458" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="459" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A459">
+        <v>61503</v>
+      </c>
+      <c r="B459" t="s">
+        <v>13</v>
+      </c>
+      <c r="C459" t="s">
+        <v>14</v>
+      </c>
+      <c r="D459" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="460" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A460">
+        <v>61504</v>
+      </c>
+      <c r="B460" t="s">
+        <v>13</v>
+      </c>
+      <c r="C460" t="s">
+        <v>14</v>
+      </c>
+      <c r="D460" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="461" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A461">
+        <v>61547</v>
+      </c>
+      <c r="B461" t="s">
+        <v>4</v>
+      </c>
+      <c r="C461" t="s">
+        <v>5</v>
+      </c>
+      <c r="D461" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="462" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A462">
+        <v>61621</v>
+      </c>
+      <c r="B462" t="s">
+        <v>4</v>
+      </c>
+      <c r="C462" t="s">
+        <v>5</v>
+      </c>
+      <c r="D462" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="463" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A463">
+        <v>61680</v>
+      </c>
+      <c r="B463" t="s">
+        <v>13</v>
+      </c>
+      <c r="C463" t="s">
+        <v>14</v>
+      </c>
+      <c r="D463" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="464" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A464">
+        <v>61691</v>
+      </c>
+      <c r="B464" t="s">
+        <v>13</v>
+      </c>
+      <c r="C464" t="s">
+        <v>14</v>
+      </c>
+      <c r="D464" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="465" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A465">
+        <v>61735</v>
+      </c>
+      <c r="B465" t="s">
+        <v>4</v>
+      </c>
+      <c r="C465" t="s">
+        <v>5</v>
+      </c>
+      <c r="D465" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="466" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A466">
+        <v>61845</v>
+      </c>
+      <c r="B466" t="s">
+        <v>4</v>
+      </c>
+      <c r="C466" t="s">
+        <v>5</v>
+      </c>
+      <c r="D466" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="467" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A467">
+        <v>61970</v>
+      </c>
+      <c r="B467" t="s">
+        <v>4</v>
+      </c>
+      <c r="C467" t="s">
+        <v>5</v>
+      </c>
+      <c r="D467" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="468" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A468">
+        <v>62378</v>
+      </c>
+      <c r="B468" t="s">
+        <v>13</v>
+      </c>
+      <c r="C468" t="s">
+        <v>14</v>
+      </c>
+      <c r="D468" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="469" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A469">
+        <v>62409</v>
+      </c>
+      <c r="B469" t="s">
+        <v>4</v>
+      </c>
+      <c r="C469" t="s">
+        <v>5</v>
+      </c>
+      <c r="D469" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="470" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A470">
+        <v>62412</v>
+      </c>
+      <c r="B470" t="s">
+        <v>4</v>
+      </c>
+      <c r="C470" t="s">
+        <v>5</v>
+      </c>
+      <c r="D470" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="471" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A471">
+        <v>62538</v>
+      </c>
+      <c r="B471" t="s">
+        <v>4</v>
+      </c>
+      <c r="C471" t="s">
+        <v>5</v>
+      </c>
+      <c r="D471" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="472" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A472">
+        <v>62549</v>
+      </c>
+      <c r="B472" t="s">
+        <v>13</v>
+      </c>
+      <c r="C472" t="s">
+        <v>14</v>
+      </c>
+      <c r="D472" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="473" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A473">
+        <v>62562</v>
+      </c>
+      <c r="B473" t="s">
+        <v>13</v>
+      </c>
+      <c r="C473" t="s">
+        <v>14</v>
+      </c>
+      <c r="D473" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="474" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A474">
+        <v>62780</v>
+      </c>
+      <c r="B474" t="s">
+        <v>4</v>
+      </c>
+      <c r="C474" t="s">
+        <v>5</v>
+      </c>
+      <c r="D474" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="475" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A475">
+        <v>62781</v>
+      </c>
+      <c r="B475" t="s">
+        <v>4</v>
+      </c>
+      <c r="C475" t="s">
+        <v>5</v>
+      </c>
+      <c r="D475" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="476" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A476">
+        <v>62782</v>
+      </c>
+      <c r="B476" t="s">
+        <v>4</v>
+      </c>
+      <c r="C476" t="s">
+        <v>5</v>
+      </c>
+      <c r="D476" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="477" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A477">
+        <v>62783</v>
+      </c>
+      <c r="B477" t="s">
+        <v>4</v>
+      </c>
+      <c r="C477" t="s">
+        <v>5</v>
+      </c>
+      <c r="D477" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="478" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A478">
+        <v>62816</v>
+      </c>
+      <c r="B478" t="s">
+        <v>4</v>
+      </c>
+      <c r="C478" t="s">
+        <v>5</v>
+      </c>
+      <c r="D478" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="479" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A479">
+        <v>62923</v>
+      </c>
+      <c r="B479" t="s">
+        <v>4</v>
+      </c>
+      <c r="C479" t="s">
+        <v>5</v>
+      </c>
+      <c r="D479" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="480" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A480">
+        <v>62924</v>
+      </c>
+      <c r="B480" t="s">
+        <v>4</v>
+      </c>
+      <c r="C480" t="s">
+        <v>5</v>
+      </c>
+      <c r="D480" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="481" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A481">
+        <v>62940</v>
+      </c>
+      <c r="B481" t="s">
+        <v>4</v>
+      </c>
+      <c r="C481" t="s">
+        <v>5</v>
+      </c>
+      <c r="D481" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="482" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A482">
+        <v>63130</v>
+      </c>
+      <c r="B482" t="s">
+        <v>4</v>
+      </c>
+      <c r="C482" t="s">
+        <v>5</v>
+      </c>
+      <c r="D482" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="483" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A483">
+        <v>63213</v>
+      </c>
+      <c r="B483" t="s">
+        <v>4</v>
+      </c>
+      <c r="C483" t="s">
+        <v>5</v>
+      </c>
+      <c r="D483" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="484" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A484">
+        <v>63214</v>
+      </c>
+      <c r="B484" t="s">
+        <v>4</v>
+      </c>
+      <c r="C484" t="s">
+        <v>5</v>
+      </c>
+      <c r="D484" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="485" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A485">
+        <v>63327</v>
+      </c>
+      <c r="B485" t="s">
+        <v>4</v>
+      </c>
+      <c r="C485" t="s">
+        <v>5</v>
+      </c>
+      <c r="D485" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="486" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A486">
+        <v>63470</v>
+      </c>
+      <c r="B486" t="s">
+        <v>4</v>
+      </c>
+      <c r="C486" t="s">
+        <v>5</v>
+      </c>
+      <c r="D486" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="487" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A487">
+        <v>63471</v>
+      </c>
+      <c r="B487" t="s">
+        <v>4</v>
+      </c>
+      <c r="C487" t="s">
+        <v>5</v>
+      </c>
+      <c r="D487" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="488" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A488">
+        <v>63488</v>
+      </c>
+      <c r="B488" t="s">
+        <v>13</v>
+      </c>
+      <c r="C488" t="s">
+        <v>14</v>
+      </c>
+      <c r="D488" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="489" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A489">
+        <v>63588</v>
+      </c>
+      <c r="B489" t="s">
+        <v>4</v>
+      </c>
+      <c r="C489" t="s">
+        <v>5</v>
+      </c>
+      <c r="D489" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="490" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A490">
+        <v>63604</v>
+      </c>
+      <c r="B490" t="s">
+        <v>13</v>
+      </c>
+      <c r="C490" t="s">
+        <v>14</v>
+      </c>
+      <c r="D490" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="491" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A491">
+        <v>63605</v>
+      </c>
+      <c r="B491" t="s">
+        <v>13</v>
+      </c>
+      <c r="C491" t="s">
+        <v>14</v>
+      </c>
+      <c r="D491" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="492" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A492">
+        <v>63606</v>
+      </c>
+      <c r="B492" t="s">
+        <v>4</v>
+      </c>
+      <c r="C492" t="s">
+        <v>5</v>
+      </c>
+      <c r="D492" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="493" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A493">
+        <v>63608</v>
+      </c>
+      <c r="B493" t="s">
+        <v>4</v>
+      </c>
+      <c r="C493" t="s">
+        <v>5</v>
+      </c>
+      <c r="D493" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="494" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A494">
+        <v>63609</v>
+      </c>
+      <c r="B494" t="s">
+        <v>4</v>
+      </c>
+      <c r="C494" t="s">
+        <v>5</v>
+      </c>
+      <c r="D494" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="495" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A495">
+        <v>63610</v>
+      </c>
+      <c r="B495" t="s">
+        <v>4</v>
+      </c>
+      <c r="C495" t="s">
+        <v>5</v>
+      </c>
+      <c r="D495" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="496" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A496">
+        <v>63771</v>
+      </c>
+      <c r="B496" t="s">
+        <v>4</v>
+      </c>
+      <c r="C496" t="s">
+        <v>5</v>
+      </c>
+      <c r="D496" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="497" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A497">
+        <v>64022</v>
+      </c>
+      <c r="B497" t="s">
+        <v>4</v>
+      </c>
+      <c r="C497" t="s">
+        <v>5</v>
+      </c>
+      <c r="D497" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="498" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A498">
+        <v>64023</v>
+      </c>
+      <c r="B498" t="s">
+        <v>4</v>
+      </c>
+      <c r="C498" t="s">
+        <v>5</v>
+      </c>
+      <c r="D498" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="499" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A499">
+        <v>64079</v>
+      </c>
+      <c r="B499" t="s">
+        <v>4</v>
+      </c>
+      <c r="C499" t="s">
+        <v>5</v>
+      </c>
+      <c r="D499" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="500" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A500">
+        <v>64130</v>
+      </c>
+      <c r="B500" t="s">
+        <v>4</v>
+      </c>
+      <c r="C500" t="s">
+        <v>5</v>
+      </c>
+      <c r="D500" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="501" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A501">
+        <v>64528</v>
+      </c>
+      <c r="B501" t="s">
+        <v>4</v>
+      </c>
+      <c r="C501" t="s">
+        <v>5</v>
+      </c>
+      <c r="D501" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="502" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A502">
+        <v>64529</v>
+      </c>
+      <c r="B502" t="s">
+        <v>4</v>
+      </c>
+      <c r="C502" t="s">
+        <v>5</v>
+      </c>
+      <c r="D502" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="503" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A503">
+        <v>64530</v>
+      </c>
+      <c r="B503" t="s">
+        <v>4</v>
+      </c>
+      <c r="C503" t="s">
+        <v>5</v>
+      </c>
+      <c r="D503" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="504" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A504">
+        <v>64589</v>
+      </c>
+      <c r="B504" t="s">
+        <v>4</v>
+      </c>
+      <c r="C504" t="s">
+        <v>5</v>
+      </c>
+      <c r="D504" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="505" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A505">
+        <v>64590</v>
+      </c>
+      <c r="B505" t="s">
+        <v>4</v>
+      </c>
+      <c r="C505" t="s">
+        <v>5</v>
+      </c>
+      <c r="D505" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="506" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A506">
+        <v>64591</v>
+      </c>
+      <c r="B506" t="s">
+        <v>4</v>
+      </c>
+      <c r="C506" t="s">
+        <v>5</v>
+      </c>
+      <c r="D506" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="507" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A507">
+        <v>64592</v>
+      </c>
+      <c r="B507" t="s">
+        <v>4</v>
+      </c>
+      <c r="C507" t="s">
+        <v>5</v>
+      </c>
+      <c r="D507" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="508" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A508">
+        <v>64593</v>
+      </c>
+      <c r="B508" t="s">
+        <v>4</v>
+      </c>
+      <c r="C508" t="s">
+        <v>5</v>
+      </c>
+      <c r="D508" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="509" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A509">
+        <v>64595</v>
+      </c>
+      <c r="B509" t="s">
+        <v>4</v>
+      </c>
+      <c r="C509" t="s">
+        <v>5</v>
+      </c>
+      <c r="D509" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="510" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A510">
+        <v>64604</v>
+      </c>
+      <c r="B510" t="s">
+        <v>13</v>
+      </c>
+      <c r="C510" t="s">
+        <v>14</v>
+      </c>
+      <c r="D510" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="511" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A511">
+        <v>64646</v>
+      </c>
+      <c r="B511" t="s">
+        <v>4</v>
+      </c>
+      <c r="C511" t="s">
+        <v>5</v>
+      </c>
+      <c r="D511" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="512" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A512">
+        <v>64694</v>
+      </c>
+      <c r="B512" t="s">
+        <v>4</v>
+      </c>
+      <c r="C512" t="s">
+        <v>5</v>
+      </c>
+      <c r="D512" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="513" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A513">
+        <v>65006</v>
+      </c>
+      <c r="B513" t="s">
+        <v>4</v>
+      </c>
+      <c r="C513" t="s">
+        <v>5</v>
+      </c>
+      <c r="D513" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="514" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A514">
+        <v>65007</v>
+      </c>
+      <c r="B514" t="s">
+        <v>4</v>
+      </c>
+      <c r="C514" t="s">
+        <v>5</v>
+      </c>
+      <c r="D514" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="515" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A515">
+        <v>65008</v>
+      </c>
+      <c r="B515" t="s">
+        <v>4</v>
+      </c>
+      <c r="C515" t="s">
+        <v>5</v>
+      </c>
+      <c r="D515" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="516" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A516">
+        <v>65214</v>
+      </c>
+      <c r="B516" t="s">
+        <v>4</v>
+      </c>
+      <c r="C516" t="s">
+        <v>5</v>
+      </c>
+      <c r="D516" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="517" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A517">
+        <v>65347</v>
+      </c>
+      <c r="B517" t="s">
+        <v>4</v>
+      </c>
+      <c r="C517" t="s">
+        <v>5</v>
+      </c>
+      <c r="D517" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="518" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A518">
+        <v>65375</v>
+      </c>
+      <c r="B518" t="s">
+        <v>4</v>
+      </c>
+      <c r="C518" t="s">
+        <v>5</v>
+      </c>
+      <c r="D518" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="519" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A519">
+        <v>65427</v>
+      </c>
+      <c r="B519" t="s">
+        <v>4</v>
+      </c>
+      <c r="C519" t="s">
+        <v>5</v>
+      </c>
+      <c r="D519" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="520" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A520">
+        <v>65506</v>
+      </c>
+      <c r="B520" t="s">
+        <v>4</v>
+      </c>
+      <c r="C520" t="s">
+        <v>5</v>
+      </c>
+      <c r="D520" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="521" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A521">
+        <v>65516</v>
+      </c>
+      <c r="B521" t="s">
+        <v>13</v>
+      </c>
+      <c r="C521" t="s">
+        <v>14</v>
+      </c>
+      <c r="D521" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="522" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A522">
+        <v>65517</v>
+      </c>
+      <c r="B522" t="s">
+        <v>13</v>
+      </c>
+      <c r="C522" t="s">
+        <v>14</v>
+      </c>
+      <c r="D522" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="523" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A523">
+        <v>65657</v>
+      </c>
+      <c r="B523" t="s">
+        <v>4</v>
+      </c>
+      <c r="C523" t="s">
+        <v>5</v>
+      </c>
+      <c r="D523" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="524" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A524">
+        <v>65658</v>
+      </c>
+      <c r="B524" t="s">
+        <v>4</v>
+      </c>
+      <c r="C524" t="s">
+        <v>5</v>
+      </c>
+      <c r="D524" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="525" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A525">
+        <v>65670</v>
+      </c>
+      <c r="B525" t="s">
+        <v>4</v>
+      </c>
+      <c r="C525" t="s">
+        <v>5</v>
+      </c>
+      <c r="D525" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="526" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A526">
+        <v>65797</v>
+      </c>
+      <c r="B526" t="s">
+        <v>4</v>
+      </c>
+      <c r="C526" t="s">
+        <v>5</v>
+      </c>
+      <c r="D526" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="527" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A527">
+        <v>65891</v>
+      </c>
+      <c r="B527" t="s">
+        <v>4</v>
+      </c>
+      <c r="C527" t="s">
+        <v>5</v>
+      </c>
+      <c r="D527" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="528" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A528">
+        <v>65909</v>
+      </c>
+      <c r="B528" t="s">
+        <v>4</v>
+      </c>
+      <c r="C528" t="s">
+        <v>5</v>
+      </c>
+      <c r="D528" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="529" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A529">
+        <v>65917</v>
+      </c>
+      <c r="B529" t="s">
+        <v>4</v>
+      </c>
+      <c r="C529" t="s">
+        <v>5</v>
+      </c>
+      <c r="D529" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="530" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A530">
+        <v>65918</v>
+      </c>
+      <c r="B530" t="s">
+        <v>4</v>
+      </c>
+      <c r="C530" t="s">
+        <v>5</v>
+      </c>
+      <c r="D530" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="531" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A531">
+        <v>66000</v>
+      </c>
+      <c r="B531" t="s">
+        <v>4</v>
+      </c>
+      <c r="C531" t="s">
+        <v>5</v>
+      </c>
+      <c r="D531" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="532" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A532">
+        <v>66072</v>
+      </c>
+      <c r="B532" t="s">
+        <v>13</v>
+      </c>
+      <c r="C532" t="s">
+        <v>14</v>
+      </c>
+      <c r="D532" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="533" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A533">
+        <v>66090</v>
+      </c>
+      <c r="B533" t="s">
+        <v>4</v>
+      </c>
+      <c r="C533" t="s">
+        <v>5</v>
+      </c>
+      <c r="D533" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="534" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A534">
+        <v>66116</v>
+      </c>
+      <c r="B534" t="s">
+        <v>13</v>
+      </c>
+      <c r="C534" t="s">
+        <v>14</v>
+      </c>
+      <c r="D534" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="535" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A535">
+        <v>66117</v>
+      </c>
+      <c r="B535" t="s">
+        <v>13</v>
+      </c>
+      <c r="C535" t="s">
+        <v>14</v>
+      </c>
+      <c r="D535" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="536" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A536">
+        <v>66146</v>
+      </c>
+      <c r="B536" t="s">
+        <v>4</v>
+      </c>
+      <c r="C536" t="s">
+        <v>5</v>
+      </c>
+      <c r="D536" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="537" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A537">
+        <v>66147</v>
+      </c>
+      <c r="B537" t="s">
+        <v>4</v>
+      </c>
+      <c r="C537" t="s">
+        <v>5</v>
+      </c>
+      <c r="D537" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="538" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A538">
+        <v>66402</v>
+      </c>
+      <c r="B538" t="s">
+        <v>4</v>
+      </c>
+      <c r="C538" t="s">
+        <v>5</v>
+      </c>
+      <c r="D538" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="539" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A539">
+        <v>66403</v>
+      </c>
+      <c r="B539" t="s">
+        <v>4</v>
+      </c>
+      <c r="C539" t="s">
+        <v>5</v>
+      </c>
+      <c r="D539" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="540" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A540">
+        <v>66404</v>
+      </c>
+      <c r="B540" t="s">
+        <v>4</v>
+      </c>
+      <c r="C540" t="s">
+        <v>5</v>
+      </c>
+      <c r="D540" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="541" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A541">
+        <v>66409</v>
+      </c>
+      <c r="B541" t="s">
+        <v>4</v>
+      </c>
+      <c r="C541" t="s">
+        <v>5</v>
+      </c>
+      <c r="D541" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="542" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A542">
+        <v>66564</v>
+      </c>
+      <c r="B542" t="s">
+        <v>4</v>
+      </c>
+      <c r="C542" t="s">
+        <v>5</v>
+      </c>
+      <c r="D542" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="543" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A543">
+        <v>66565</v>
+      </c>
+      <c r="B543" t="s">
+        <v>4</v>
+      </c>
+      <c r="C543" t="s">
+        <v>5</v>
+      </c>
+      <c r="D543" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="544" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A544">
+        <v>66587</v>
+      </c>
+      <c r="B544" t="s">
+        <v>4</v>
+      </c>
+      <c r="C544" t="s">
+        <v>5</v>
+      </c>
+      <c r="D544" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="545" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A545">
+        <v>66680</v>
+      </c>
+      <c r="B545" t="s">
+        <v>4</v>
+      </c>
+      <c r="C545" t="s">
+        <v>5</v>
+      </c>
+      <c r="D545" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="546" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A546">
+        <v>66810</v>
+      </c>
+      <c r="B546" t="s">
+        <v>4</v>
+      </c>
+      <c r="C546" t="s">
+        <v>5</v>
+      </c>
+      <c r="D546" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="547" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A547">
+        <v>66884</v>
+      </c>
+      <c r="B547" t="s">
+        <v>4</v>
+      </c>
+      <c r="C547" t="s">
+        <v>5</v>
+      </c>
+      <c r="D547" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="548" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A548">
+        <v>66912</v>
+      </c>
+      <c r="B548" t="s">
+        <v>4</v>
+      </c>
+      <c r="C548" t="s">
+        <v>5</v>
+      </c>
+      <c r="D548" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="549" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A549">
+        <v>66930</v>
+      </c>
+      <c r="B549" t="s">
+        <v>4</v>
+      </c>
+      <c r="C549" t="s">
+        <v>5</v>
+      </c>
+      <c r="D549" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="550" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A550">
+        <v>67331</v>
+      </c>
+      <c r="B550" t="s">
+        <v>4</v>
+      </c>
+      <c r="C550" t="s">
+        <v>5</v>
+      </c>
+      <c r="D550" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="551" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A551">
+        <v>67353</v>
+      </c>
+      <c r="B551" t="s">
+        <v>4</v>
+      </c>
+      <c r="C551" t="s">
+        <v>5</v>
+      </c>
+      <c r="D551" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="552" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A552">
+        <v>67354</v>
+      </c>
+      <c r="B552" t="s">
+        <v>4</v>
+      </c>
+      <c r="C552" t="s">
+        <v>5</v>
+      </c>
+      <c r="D552" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="553" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A553">
+        <v>67366</v>
+      </c>
+      <c r="B553" t="s">
+        <v>13</v>
+      </c>
+      <c r="C553" t="s">
+        <v>14</v>
+      </c>
+      <c r="D553" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="554" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A554">
+        <v>67388</v>
+      </c>
+      <c r="B554" t="s">
+        <v>4</v>
+      </c>
+      <c r="C554" t="s">
+        <v>5</v>
+      </c>
+      <c r="D554" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="555" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A555">
+        <v>67402</v>
+      </c>
+      <c r="B555" t="s">
+        <v>4</v>
+      </c>
+      <c r="C555" t="s">
+        <v>5</v>
+      </c>
+      <c r="D555" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="556" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A556">
+        <v>67510</v>
+      </c>
+      <c r="B556" t="s">
+        <v>4</v>
+      </c>
+      <c r="C556" t="s">
+        <v>5</v>
+      </c>
+      <c r="D556" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="557" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A557">
+        <v>67511</v>
+      </c>
+      <c r="B557" t="s">
+        <v>4</v>
+      </c>
+      <c r="C557" t="s">
+        <v>5</v>
+      </c>
+      <c r="D557" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="558" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A558">
+        <v>67532</v>
+      </c>
+      <c r="B558" t="s">
+        <v>4</v>
+      </c>
+      <c r="C558" t="s">
+        <v>5</v>
+      </c>
+      <c r="D558" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="559" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A559">
+        <v>67676</v>
+      </c>
+      <c r="B559" t="s">
+        <v>4</v>
+      </c>
+      <c r="C559" t="s">
+        <v>5</v>
+      </c>
+      <c r="D559" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="560" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A560">
+        <v>67865</v>
+      </c>
+      <c r="B560" t="s">
+        <v>4</v>
+      </c>
+      <c r="C560" t="s">
+        <v>5</v>
+      </c>
+      <c r="D560" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="561" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A561">
+        <v>67935</v>
+      </c>
+      <c r="B561" t="s">
+        <v>4</v>
+      </c>
+      <c r="C561" t="s">
+        <v>5</v>
+      </c>
+      <c r="D561" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="562" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A562">
+        <v>67944</v>
+      </c>
+      <c r="B562" t="s">
+        <v>4</v>
+      </c>
+      <c r="C562" t="s">
+        <v>5</v>
+      </c>
+      <c r="D562" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="563" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A563">
+        <v>67945</v>
+      </c>
+      <c r="B563" t="s">
+        <v>4</v>
+      </c>
+      <c r="C563" t="s">
+        <v>5</v>
+      </c>
+      <c r="D563" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="564" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A564">
+        <v>67946</v>
+      </c>
+      <c r="B564" t="s">
+        <v>4</v>
+      </c>
+      <c r="C564" t="s">
+        <v>5</v>
+      </c>
+      <c r="D564" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="565" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A565">
+        <v>67947</v>
+      </c>
+      <c r="B565" t="s">
+        <v>13</v>
+      </c>
+      <c r="C565" t="s">
+        <v>14</v>
+      </c>
+      <c r="D565" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="566" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A566">
+        <v>67970</v>
+      </c>
+      <c r="B566" t="s">
+        <v>4</v>
+      </c>
+      <c r="C566" t="s">
+        <v>5</v>
+      </c>
+      <c r="D566" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="567" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A567">
+        <v>67980</v>
+      </c>
+      <c r="B567" t="s">
+        <v>4</v>
+      </c>
+      <c r="C567" t="s">
+        <v>5</v>
+      </c>
+      <c r="D567" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="568" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A568">
+        <v>67985</v>
+      </c>
+      <c r="B568" t="s">
+        <v>4</v>
+      </c>
+      <c r="C568" t="s">
+        <v>5</v>
+      </c>
+      <c r="D568" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="569" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A569">
+        <v>67990</v>
+      </c>
+      <c r="B569" t="s">
+        <v>4</v>
+      </c>
+      <c r="C569" t="s">
+        <v>5</v>
+      </c>
+      <c r="D569" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="570" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A570">
+        <v>67991</v>
+      </c>
+      <c r="B570" t="s">
+        <v>4</v>
+      </c>
+      <c r="C570" t="s">
+        <v>5</v>
+      </c>
+      <c r="D570" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="571" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A571">
+        <v>68031</v>
+      </c>
+      <c r="B571" t="s">
+        <v>4</v>
+      </c>
+      <c r="C571" t="s">
+        <v>5</v>
+      </c>
+      <c r="D571" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="572" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A572">
+        <v>68032</v>
+      </c>
+      <c r="B572" t="s">
+        <v>4</v>
+      </c>
+      <c r="C572" t="s">
+        <v>5</v>
+      </c>
+      <c r="D572" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="573" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A573">
+        <v>68114</v>
+      </c>
+      <c r="B573" t="s">
+        <v>4</v>
+      </c>
+      <c r="C573" t="s">
+        <v>5</v>
+      </c>
+      <c r="D573" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="574" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A574">
+        <v>68160</v>
+      </c>
+      <c r="B574" t="s">
+        <v>4</v>
+      </c>
+      <c r="C574" t="s">
+        <v>5</v>
+      </c>
+      <c r="D574" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="575" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A575">
+        <v>68171</v>
+      </c>
+      <c r="B575" t="s">
+        <v>4</v>
+      </c>
+      <c r="C575" t="s">
+        <v>5</v>
+      </c>
+      <c r="D575" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="576" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A576">
+        <v>68172</v>
+      </c>
+      <c r="B576" t="s">
+        <v>4</v>
+      </c>
+      <c r="C576" t="s">
+        <v>5</v>
+      </c>
+      <c r="D576" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="577" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A577">
+        <v>68173</v>
+      </c>
+      <c r="B577" t="s">
+        <v>4</v>
+      </c>
+      <c r="C577" t="s">
+        <v>5</v>
+      </c>
+      <c r="D577" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="578" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A578">
+        <v>68214</v>
+      </c>
+      <c r="B578" t="s">
+        <v>4</v>
+      </c>
+      <c r="C578" t="s">
+        <v>5</v>
+      </c>
+      <c r="D578" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="579" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A579">
+        <v>68215</v>
+      </c>
+      <c r="B579" t="s">
+        <v>4</v>
+      </c>
+      <c r="C579" t="s">
+        <v>5</v>
+      </c>
+      <c r="D579" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="580" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A580">
+        <v>68216</v>
+      </c>
+      <c r="B580" t="s">
+        <v>4</v>
+      </c>
+      <c r="C580" t="s">
+        <v>5</v>
+      </c>
+      <c r="D580" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="581" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A581">
+        <v>68328</v>
+      </c>
+      <c r="B581" t="s">
+        <v>4</v>
+      </c>
+      <c r="C581" t="s">
+        <v>5</v>
+      </c>
+      <c r="D581" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="582" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A582">
+        <v>68329</v>
+      </c>
+      <c r="B582" t="s">
+        <v>4</v>
+      </c>
+      <c r="C582" t="s">
+        <v>5</v>
+      </c>
+      <c r="D582" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="583" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A583">
+        <v>68330</v>
+      </c>
+      <c r="B583" t="s">
+        <v>4</v>
+      </c>
+      <c r="C583" t="s">
+        <v>5</v>
+      </c>
+      <c r="D583" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="584" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A584">
+        <v>68331</v>
+      </c>
+      <c r="B584" t="s">
+        <v>4</v>
+      </c>
+      <c r="C584" t="s">
+        <v>5</v>
+      </c>
+      <c r="D584" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="585" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A585">
+        <v>68366</v>
+      </c>
+      <c r="B585" t="s">
+        <v>4</v>
+      </c>
+      <c r="C585" t="s">
+        <v>5</v>
+      </c>
+      <c r="D585" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="586" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A586">
+        <v>68374</v>
+      </c>
+      <c r="B586" t="s">
+        <v>4</v>
+      </c>
+      <c r="C586" t="s">
+        <v>5</v>
+      </c>
+      <c r="D586" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="587" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A587">
+        <v>68482</v>
+      </c>
+      <c r="B587" t="s">
+        <v>4</v>
+      </c>
+      <c r="C587" t="s">
+        <v>5</v>
+      </c>
+      <c r="D587" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="588" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A588">
+        <v>68510</v>
+      </c>
+      <c r="B588" t="s">
+        <v>4</v>
+      </c>
+      <c r="C588" t="s">
+        <v>5</v>
+      </c>
+      <c r="D588" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="589" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A589">
+        <v>68517</v>
+      </c>
+      <c r="B589" t="s">
+        <v>4</v>
+      </c>
+      <c r="C589" t="s">
+        <v>5</v>
+      </c>
+      <c r="D589" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="590" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A590">
+        <v>68531</v>
+      </c>
+      <c r="B590" t="s">
+        <v>4</v>
+      </c>
+      <c r="C590" t="s">
+        <v>5</v>
+      </c>
+      <c r="D590" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="591" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A591">
+        <v>68711</v>
+      </c>
+      <c r="B591" t="s">
+        <v>4</v>
+      </c>
+      <c r="C591" t="s">
+        <v>5</v>
+      </c>
+      <c r="D591" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="592" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A592">
+        <v>68746</v>
+      </c>
+      <c r="B592" t="s">
+        <v>4</v>
+      </c>
+      <c r="C592" t="s">
+        <v>5</v>
+      </c>
+      <c r="D592" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="593" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A593">
+        <v>68751</v>
+      </c>
+      <c r="B593" t="s">
+        <v>4</v>
+      </c>
+      <c r="C593" t="s">
+        <v>5</v>
+      </c>
+      <c r="D593" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="594" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A594">
+        <v>68819</v>
+      </c>
+      <c r="B594" t="s">
+        <v>4</v>
+      </c>
+      <c r="C594" t="s">
+        <v>5</v>
+      </c>
+      <c r="D594" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="595" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A595">
+        <v>68862</v>
+      </c>
+      <c r="B595" t="s">
+        <v>4</v>
+      </c>
+      <c r="C595" t="s">
+        <v>5</v>
+      </c>
+      <c r="D595" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="596" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A596">
+        <v>68987</v>
+      </c>
+      <c r="B596" t="s">
+        <v>4</v>
+      </c>
+      <c r="C596" t="s">
+        <v>5</v>
+      </c>
+      <c r="D596" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="597" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A597">
+        <v>69038</v>
+      </c>
+      <c r="B597" t="s">
+        <v>13</v>
+      </c>
+      <c r="C597" t="s">
+        <v>14</v>
+      </c>
+      <c r="D597" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="598" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A598">
+        <v>69039</v>
+      </c>
+      <c r="B598" t="s">
+        <v>13</v>
+      </c>
+      <c r="C598" t="s">
+        <v>14</v>
+      </c>
+      <c r="D598" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="599" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A599">
+        <v>69041</v>
+      </c>
+      <c r="B599" t="s">
+        <v>4</v>
+      </c>
+      <c r="C599" t="s">
+        <v>5</v>
+      </c>
+      <c r="D599" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="600" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A600">
+        <v>69164</v>
+      </c>
+      <c r="B600" t="s">
+        <v>4</v>
+      </c>
+      <c r="C600" t="s">
+        <v>5</v>
+      </c>
+      <c r="D600" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="601" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A601">
+        <v>69165</v>
+      </c>
+      <c r="B601" t="s">
+        <v>4</v>
+      </c>
+      <c r="C601" t="s">
+        <v>5</v>
+      </c>
+      <c r="D601" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="602" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A602">
+        <v>69212</v>
+      </c>
+      <c r="B602" t="s">
+        <v>13</v>
+      </c>
+      <c r="C602" t="s">
+        <v>14</v>
+      </c>
+      <c r="D602" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="603" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A603">
+        <v>69282</v>
+      </c>
+      <c r="B603" t="s">
+        <v>4</v>
+      </c>
+      <c r="C603" t="s">
+        <v>5</v>
+      </c>
+      <c r="D603" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="604" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A604">
+        <v>69283</v>
+      </c>
+      <c r="B604" t="s">
+        <v>4</v>
+      </c>
+      <c r="C604" t="s">
+        <v>5</v>
+      </c>
+      <c r="D604" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="605" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A605">
+        <v>69312</v>
+      </c>
+      <c r="B605" t="s">
+        <v>13</v>
+      </c>
+      <c r="C605" t="s">
+        <v>14</v>
+      </c>
+      <c r="D605" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="606" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A606">
+        <v>69396</v>
+      </c>
+      <c r="B606" t="s">
+        <v>4</v>
+      </c>
+      <c r="C606" t="s">
+        <v>5</v>
+      </c>
+      <c r="D606" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="607" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A607">
+        <v>69407</v>
+      </c>
+      <c r="B607" t="s">
+        <v>4</v>
+      </c>
+      <c r="C607" t="s">
+        <v>5</v>
+      </c>
+      <c r="D607" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="608" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A608">
+        <v>69408</v>
+      </c>
+      <c r="B608" t="s">
+        <v>13</v>
+      </c>
+      <c r="C608" t="s">
+        <v>14</v>
+      </c>
+      <c r="D608" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="609" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A609">
+        <v>69555</v>
+      </c>
+      <c r="B609" t="s">
+        <v>4</v>
+      </c>
+      <c r="C609" t="s">
+        <v>5</v>
+      </c>
+      <c r="D609" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="610" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A610">
+        <v>69556</v>
+      </c>
+      <c r="B610" t="s">
+        <v>4</v>
+      </c>
+      <c r="C610" t="s">
+        <v>5</v>
+      </c>
+      <c r="D610" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="611" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A611">
+        <v>69582</v>
+      </c>
+      <c r="B611" t="s">
+        <v>4</v>
+      </c>
+      <c r="C611" t="s">
+        <v>5</v>
+      </c>
+      <c r="D611" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="612" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A612">
+        <v>69631</v>
+      </c>
+      <c r="B612" t="s">
+        <v>13</v>
+      </c>
+      <c r="C612" t="s">
+        <v>14</v>
+      </c>
+      <c r="D612" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="613" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A613">
+        <v>69682</v>
+      </c>
+      <c r="B613" t="s">
+        <v>13</v>
+      </c>
+      <c r="C613" t="s">
+        <v>14</v>
+      </c>
+      <c r="D613" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="614" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A614">
+        <v>69683</v>
+      </c>
+      <c r="B614" t="s">
+        <v>13</v>
+      </c>
+      <c r="C614" t="s">
+        <v>14</v>
+      </c>
+      <c r="D614" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="615" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A615">
+        <v>69692</v>
+      </c>
+      <c r="B615" t="s">
+        <v>4</v>
+      </c>
+      <c r="C615" t="s">
+        <v>5</v>
+      </c>
+      <c r="D615" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="616" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A616">
+        <v>69703</v>
+      </c>
+      <c r="B616" t="s">
+        <v>13</v>
+      </c>
+      <c r="C616" t="s">
+        <v>14</v>
+      </c>
+      <c r="D616" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="617" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A617">
+        <v>69873</v>
+      </c>
+      <c r="B617" t="s">
+        <v>4</v>
+      </c>
+      <c r="C617" t="s">
+        <v>5</v>
+      </c>
+      <c r="D617" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="618" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A618">
+        <v>69927</v>
+      </c>
+      <c r="B618" t="s">
+        <v>4</v>
+      </c>
+      <c r="C618" t="s">
+        <v>5</v>
+      </c>
+      <c r="D618" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="619" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A619">
+        <v>69928</v>
+      </c>
+      <c r="B619" t="s">
+        <v>4</v>
+      </c>
+      <c r="C619" t="s">
+        <v>5</v>
+      </c>
+      <c r="D619" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="620" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A620">
+        <v>69929</v>
+      </c>
+      <c r="B620" t="s">
+        <v>4</v>
+      </c>
+      <c r="C620" t="s">
+        <v>5</v>
+      </c>
+      <c r="D620" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="621" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A621">
+        <v>70137</v>
+      </c>
+      <c r="B621" t="s">
+        <v>4</v>
+      </c>
+      <c r="C621" t="s">
+        <v>5</v>
+      </c>
+      <c r="D621" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="622" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A622">
+        <v>70138</v>
+      </c>
+      <c r="B622" t="s">
+        <v>4</v>
+      </c>
+      <c r="C622" t="s">
+        <v>5</v>
+      </c>
+      <c r="D622" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="623" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A623">
+        <v>70180</v>
+      </c>
+      <c r="B623" t="s">
+        <v>4</v>
+      </c>
+      <c r="C623" t="s">
+        <v>5</v>
+      </c>
+      <c r="D623" t="s">
+        <v>630</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/apps/backend/excel-data/issuereturn_library_migration.xlsx
+++ b/apps/backend/excel-data/issuereturn_library_migration.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4282" uniqueCount="1435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5008" uniqueCount="1678">
   <si>
     <t>legacy_id</t>
   </si>
@@ -4316,6 +4316,736 @@
   </si>
   <si>
     <t>2026-05-11T06:24:39.339Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:46:28.072Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:46:32.826Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:46:35.519Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:46:41.618Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:46:44.115Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:46:46.128Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:46:47.559Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:46:49.591Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:46:51.084Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:46:52.279Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:46:54.008Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:46:55.301Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:46:56.657Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:46:57.865Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:46:59.029Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:47:00.215Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:47:01.475Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:47:02.839Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:47:04.215Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:47:05.485Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:47:06.763Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:47:08.193Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:47:09.597Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:47:11.311Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:47:13.157Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:47:14.601Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:47:15.984Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:47:17.247Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:47:18.590Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:47:20.647Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:47:22.096Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:47:25.193Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:47:26.734Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:47:28.342Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:47:29.899Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:47:31.400Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:47:33.412Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:47:34.832Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:47:36.484Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:47:38.650Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:47:40.863Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:47:42.603Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:47:44.652Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:47:49.234Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:47:50.469Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:47:51.745Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:47:53.272Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:47:55.530Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:47:57.208Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:47:58.618Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:47:59.783Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:48:00.982Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:48:02.472Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:48:03.568Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:48:05.141Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:48:06.247Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:48:07.570Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:48:08.910Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:48:11.288Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:48:13.002Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:48:14.347Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:48:15.785Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:48:17.799Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:48:19.152Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:48:20.257Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:48:21.896Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:48:24.757Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:48:26.260Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:48:27.960Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:48:29.705Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:48:30.863Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:48:31.934Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:48:33.052Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:48:34.390Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:48:35.529Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:48:37.153Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:48:39.774Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:48:41.928Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:48:43.785Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:48:45.566Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:48:47.081Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:48:48.680Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:48:53.264Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:48:57.074Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:48:59.497Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:49:02.716Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:49:08.084Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:49:14.071Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:49:16.326Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:49:17.963Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:49:19.319Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:49:20.856Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:49:22.131Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:49:23.536Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:49:24.906Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:49:26.211Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:49:27.536Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:49:28.900Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:49:30.259Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:49:31.645Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:49:33.171Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:49:34.421Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:49:35.636Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:49:37.161Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:49:38.632Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:49:41.790Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:49:44.477Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:49:48.888Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:49:53.082Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:49:56.206Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:49:59.855Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:50:03.482Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:50:06.372Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:50:08.684Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:50:11.333Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:50:14.589Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:50:17.200Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:50:19.855Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:50:22.043Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:50:23.748Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:50:25.796Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:50:28.304Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:50:31.142Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:50:34.311Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:50:36.135Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:50:37.565Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:50:40.173Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:50:42.557Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:50:44.926Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:50:48.013Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:50:49.826Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:50:51.508Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:50:54.531Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:50:57.981Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:51:00.213Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:51:02.387Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:51:04.062Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:51:05.611Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:51:07.079Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:51:08.756Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:51:10.791Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:51:12.934Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:51:15.550Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:51:18.511Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:51:21.022Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:51:22.862Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:51:24.502Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:51:26.087Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:51:27.379Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:51:29.008Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:51:30.353Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:51:31.822Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:51:33.473Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:51:34.820Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:51:36.569Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:51:38.318Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:51:40.566Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:51:42.524Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:51:44.871Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:51:46.317Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:51:47.845Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:51:49.187Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:51:51.495Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:51:52.858Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:51:54.383Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:51:55.642Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:51:57.054Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:51:58.666Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:52:00.115Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:52:01.578Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:52:03.029Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:52:04.424Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:52:06.789Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:52:10.465Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:52:12.659Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:52:14.863Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:52:17.509Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:52:19.484Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:52:22.614Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:52:24.694Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:52:27.383Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:52:29.840Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:52:31.264Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:52:32.936Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:52:34.821Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:52:36.148Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:52:37.594Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:52:38.924Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:52:40.244Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:52:41.641Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:52:55.126Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:53:14.385Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:53:27.675Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:53:29.051Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:53:46.449Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:53:59.826Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:54:10.784Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:54:17.076Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:54:25.905Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Failed query: insert into "copy_details" ("id", "legacy_copy_details_id", "book_id_fk", "published_year", "access_number", "old_access_number", "type", "issue_type", "status_id_fk", "entry_mode_id_fk", "rack_id_fk", "shelf_id_fk", "voucher_number", "enclosure_id_fk", "number_of_enclosures", "number_of_pages", "price_in_inr", "price_foreign_currency", "purchase_price", "set_price", "binding_type_id_fk", "isbn", "book_volume", "book_part", "book_part_info", "volume_info", "remarks", "legacy_vendor_id", "donor_person_id_fk", "prefix", "suffix", "pdf_path", "book_size", "bill_date", "discount", "shipping_charges", "created_by_user_id_fk", "created_at", "updated_by_user_id_fk", "updated_at") values (default, $1, $2, $3, $4, $5, $6, $7, $8, $9, $10, $11, $12, default, $13, $14, $15, $16, $17, $18, $19, $20, $21, $22, $23, $24, $25, $26, default, $27, $28, $29, $30, $31, $32, $33, default, $34, default, default) returning "id", "legacy_copy_details_id", "book_id_fk", "published_year", "access_number", "old_access_number", "type", "issue_type", "status_id_fk", "entry_mode_id_fk", "rack_id_fk", "shelf_id_fk", "voucher_number", "enclosure_id_fk", "number_of_enclosures", "number_of_pages", "price_in_inr", "price_foreign_currency", "purchase_price", "set_price", "binding_type_id_fk", "isbn", "book_volume", "book_part", "book_part_info", "volume_info", "remarks", "legacy_vendor_id", "donor_person_id_fk", "prefix", "suffix", "pdf_path", "book_size", "bill_date", "discount", "shipping_charges", "created_by_user_id_fk", "created_at", "updated_by_user_id_fk", "updated_at"
+params: 20473,487,,19793,19793,Text Book,Issue Relevant,1,1,1,26,8932,0,9780571180172,450,0,0,null,1,,,,,,,5,0,0,,,2015-08-13T18:30:00.000Z,0,,2015-08-17T18:30:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:54:32.364Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:54:38.371Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:54:48.798Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:54:58.053Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:55:05.414Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:55:10.279Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:55:16.131Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:55:17.154Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:55:18.121Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:55:31.345Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:55:38.977Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:55:46.108Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:55:59.740Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:56:07.053Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:56:17.046Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:56:25.094Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:56:26.847Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:56:28.503Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:56:31.068Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:56:33.127Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:56:34.611Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:56:43.827Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:56:53.270Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:57:00.139Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:57:11.343Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:57:22.928Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:57:31.806Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:57:34.041Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:57:47.908Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:57:55.965Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:58:05.272Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:58:16.594Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:58:25.059Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:58:33.515Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:58:45.026Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:58:52.038Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:58:58.459Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:59:06.095Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:59:19.022Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:59:28.759Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:59:41.329Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:59:55.051Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T08:00:15.126Z</t>
   </si>
 </sst>
 </file>
@@ -4696,7 +5426,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1427"/>
+  <dimension ref="A1:D1669"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -24677,6 +25407,3394 @@
         <v>1434</v>
       </c>
     </row>
+    <row r="1428" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1428">
+        <v>36130</v>
+      </c>
+      <c r="B1428" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1428" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1428" t="s">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="1429" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1429">
+        <v>36982</v>
+      </c>
+      <c r="B1429" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1429" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1429" t="s">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="1430" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1430">
+        <v>37243</v>
+      </c>
+      <c r="B1430" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1430" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1430" t="s">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1431">
+        <v>38017</v>
+      </c>
+      <c r="B1431" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1431" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1431" t="s">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="1432" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1432">
+        <v>38021</v>
+      </c>
+      <c r="B1432" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1432" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1432" t="s">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="1433" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1433">
+        <v>39441</v>
+      </c>
+      <c r="B1433" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1433" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1433" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1434">
+        <v>39804</v>
+      </c>
+      <c r="B1434" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1434" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1434" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1435">
+        <v>40721</v>
+      </c>
+      <c r="B1435" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1435" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1435" t="s">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1436">
+        <v>40723</v>
+      </c>
+      <c r="B1436" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1436" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1436" t="s">
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="1437" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1437">
+        <v>40996</v>
+      </c>
+      <c r="B1437" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1437" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1437" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="1438" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1438">
+        <v>41181</v>
+      </c>
+      <c r="B1438" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1438" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1438" t="s">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="1439" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1439">
+        <v>41182</v>
+      </c>
+      <c r="B1439" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1439" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1439" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="1440" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1440">
+        <v>41696</v>
+      </c>
+      <c r="B1440" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1440" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1440" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="1441" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1441">
+        <v>41952</v>
+      </c>
+      <c r="B1441" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1441" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1441" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="1442" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1442">
+        <v>41953</v>
+      </c>
+      <c r="B1442" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1442" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1442" t="s">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="1443" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1443">
+        <v>42439</v>
+      </c>
+      <c r="B1443" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1443" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1443" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="1444" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1444">
+        <v>42669</v>
+      </c>
+      <c r="B1444" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1444" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1444" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="1445" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1445">
+        <v>42802</v>
+      </c>
+      <c r="B1445" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1445" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1445" t="s">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="1446" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1446">
+        <v>42854</v>
+      </c>
+      <c r="B1446" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1446" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1446" t="s">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="1447" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1447">
+        <v>42855</v>
+      </c>
+      <c r="B1447" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1447" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1447" t="s">
+        <v>1454</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1448">
+        <v>43251</v>
+      </c>
+      <c r="B1448" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1448" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1448" t="s">
+        <v>1455</v>
+      </c>
+    </row>
+    <row r="1449" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1449">
+        <v>43620</v>
+      </c>
+      <c r="B1449" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1449" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1449" t="s">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="1450" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1450">
+        <v>43622</v>
+      </c>
+      <c r="B1450" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1450" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1450" t="s">
+        <v>1457</v>
+      </c>
+    </row>
+    <row r="1451" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1451">
+        <v>44376</v>
+      </c>
+      <c r="B1451" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1451" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1451" t="s">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="1452" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1452">
+        <v>44632</v>
+      </c>
+      <c r="B1452" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1452" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1452" t="s">
+        <v>1459</v>
+      </c>
+    </row>
+    <row r="1453" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1453">
+        <v>44662</v>
+      </c>
+      <c r="B1453" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1453" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1453" t="s">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="1454" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1454">
+        <v>44700</v>
+      </c>
+      <c r="B1454" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1454" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1454" t="s">
+        <v>1461</v>
+      </c>
+    </row>
+    <row r="1455" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1455">
+        <v>44711</v>
+      </c>
+      <c r="B1455" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1455" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1455" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="1456" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1456">
+        <v>44859</v>
+      </c>
+      <c r="B1456" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1456" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1456" t="s">
+        <v>1463</v>
+      </c>
+    </row>
+    <row r="1457" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1457">
+        <v>46018</v>
+      </c>
+      <c r="B1457" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1457" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1457" t="s">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="1458" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1458">
+        <v>46402</v>
+      </c>
+      <c r="B1458" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1458" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1458" t="s">
+        <v>1465</v>
+      </c>
+    </row>
+    <row r="1459" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1459">
+        <v>46413</v>
+      </c>
+      <c r="B1459" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1459" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1459" t="s">
+        <v>1466</v>
+      </c>
+    </row>
+    <row r="1460" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1460">
+        <v>47141</v>
+      </c>
+      <c r="B1460" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1460" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1460" t="s">
+        <v>1467</v>
+      </c>
+    </row>
+    <row r="1461" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1461">
+        <v>47199</v>
+      </c>
+      <c r="B1461" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1461" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1461" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="1462" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1462">
+        <v>47485</v>
+      </c>
+      <c r="B1462" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1462" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1462" t="s">
+        <v>1469</v>
+      </c>
+    </row>
+    <row r="1463" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1463">
+        <v>48002</v>
+      </c>
+      <c r="B1463" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1463" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1463" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="1464" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1464">
+        <v>48003</v>
+      </c>
+      <c r="B1464" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1464" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1464" t="s">
+        <v>1471</v>
+      </c>
+    </row>
+    <row r="1465" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1465">
+        <v>48079</v>
+      </c>
+      <c r="B1465" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1465" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1465" t="s">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="1466" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1466">
+        <v>48080</v>
+      </c>
+      <c r="B1466" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1466" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1466" t="s">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="1467" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1467">
+        <v>48634</v>
+      </c>
+      <c r="B1467" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1467" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1467" t="s">
+        <v>1474</v>
+      </c>
+    </row>
+    <row r="1468" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1468">
+        <v>48758</v>
+      </c>
+      <c r="B1468" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1468" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1468" t="s">
+        <v>1475</v>
+      </c>
+    </row>
+    <row r="1469" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1469">
+        <v>48853</v>
+      </c>
+      <c r="B1469" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1469" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1469" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="1470" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1470">
+        <v>49407</v>
+      </c>
+      <c r="B1470" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1470" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1470" t="s">
+        <v>1477</v>
+      </c>
+    </row>
+    <row r="1471" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1471">
+        <v>49634</v>
+      </c>
+      <c r="B1471" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1471" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1471" t="s">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="1472" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1472">
+        <v>51146</v>
+      </c>
+      <c r="B1472" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1472" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1472" t="s">
+        <v>1479</v>
+      </c>
+    </row>
+    <row r="1473" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1473">
+        <v>51558</v>
+      </c>
+      <c r="B1473" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1473" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1473" t="s">
+        <v>1480</v>
+      </c>
+    </row>
+    <row r="1474" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1474">
+        <v>51991</v>
+      </c>
+      <c r="B1474" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1474" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1474" t="s">
+        <v>1481</v>
+      </c>
+    </row>
+    <row r="1475" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1475">
+        <v>52040</v>
+      </c>
+      <c r="B1475" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1475" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1475" t="s">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="1476" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1476">
+        <v>52187</v>
+      </c>
+      <c r="B1476" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1476" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1476" t="s">
+        <v>1483</v>
+      </c>
+    </row>
+    <row r="1477" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1477">
+        <v>52317</v>
+      </c>
+      <c r="B1477" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1477" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1477" t="s">
+        <v>1484</v>
+      </c>
+    </row>
+    <row r="1478" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1478">
+        <v>52464</v>
+      </c>
+      <c r="B1478" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1478" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1478" t="s">
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="1479" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1479">
+        <v>52465</v>
+      </c>
+      <c r="B1479" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1479" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1479" t="s">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="1480" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1480">
+        <v>52466</v>
+      </c>
+      <c r="B1480" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1480" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1480" t="s">
+        <v>1487</v>
+      </c>
+    </row>
+    <row r="1481" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1481">
+        <v>52467</v>
+      </c>
+      <c r="B1481" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1481" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1481" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="1482" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1482">
+        <v>52631</v>
+      </c>
+      <c r="B1482" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1482" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1482" t="s">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="1483" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1483">
+        <v>52635</v>
+      </c>
+      <c r="B1483" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1483" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1483" t="s">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="1484" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1484">
+        <v>52923</v>
+      </c>
+      <c r="B1484" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1484" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1484" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="1485" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1485">
+        <v>53488</v>
+      </c>
+      <c r="B1485" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1485" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1485" t="s">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="1486" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1486">
+        <v>54596</v>
+      </c>
+      <c r="B1486" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1486" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1486" t="s">
+        <v>1493</v>
+      </c>
+    </row>
+    <row r="1487" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1487">
+        <v>55299</v>
+      </c>
+      <c r="B1487" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1487" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1487" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1488" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1488">
+        <v>56209</v>
+      </c>
+      <c r="B1488" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1488" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1488" t="s">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="1489" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1489">
+        <v>56210</v>
+      </c>
+      <c r="B1489" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1489" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1489" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="1490" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1490">
+        <v>56211</v>
+      </c>
+      <c r="B1490" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1490" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1490" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="1491" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1491">
+        <v>56220</v>
+      </c>
+      <c r="B1491" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1491" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1491" t="s">
+        <v>1498</v>
+      </c>
+    </row>
+    <row r="1492" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1492">
+        <v>56221</v>
+      </c>
+      <c r="B1492" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1492" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1492" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="1493" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1493">
+        <v>56450</v>
+      </c>
+      <c r="B1493" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1493" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1493" t="s">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="1494" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1494">
+        <v>56451</v>
+      </c>
+      <c r="B1494" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1494" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1494" t="s">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="1495" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1495">
+        <v>56551</v>
+      </c>
+      <c r="B1495" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1495" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1495" t="s">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="1496" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1496">
+        <v>56552</v>
+      </c>
+      <c r="B1496" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1496" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1496" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="1497" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1497">
+        <v>56553</v>
+      </c>
+      <c r="B1497" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1497" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1497" t="s">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="1498" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1498">
+        <v>56554</v>
+      </c>
+      <c r="B1498" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1498" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1498" t="s">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="1499" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1499">
+        <v>56705</v>
+      </c>
+      <c r="B1499" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1499" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1499" t="s">
+        <v>1506</v>
+      </c>
+    </row>
+    <row r="1500" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1500">
+        <v>57031</v>
+      </c>
+      <c r="B1500" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1500" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1500" t="s">
+        <v>1507</v>
+      </c>
+    </row>
+    <row r="1501" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1501">
+        <v>57471</v>
+      </c>
+      <c r="B1501" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1501" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1501" t="s">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="1502" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1502">
+        <v>57656</v>
+      </c>
+      <c r="B1502" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1502" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1502" t="s">
+        <v>1509</v>
+      </c>
+    </row>
+    <row r="1503" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1503">
+        <v>57859</v>
+      </c>
+      <c r="B1503" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1503" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1503" t="s">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="1504" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1504">
+        <v>57860</v>
+      </c>
+      <c r="B1504" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1504" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1504" t="s">
+        <v>1511</v>
+      </c>
+    </row>
+    <row r="1505" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1505">
+        <v>58262</v>
+      </c>
+      <c r="B1505" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1505" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1505" t="s">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="1506" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1506">
+        <v>58263</v>
+      </c>
+      <c r="B1506" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1506" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1506" t="s">
+        <v>1513</v>
+      </c>
+    </row>
+    <row r="1507" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1507">
+        <v>58608</v>
+      </c>
+      <c r="B1507" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1507" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1507" t="s">
+        <v>1514</v>
+      </c>
+    </row>
+    <row r="1508" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1508">
+        <v>58614</v>
+      </c>
+      <c r="B1508" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1508" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1508" t="s">
+        <v>1515</v>
+      </c>
+    </row>
+    <row r="1509" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1509">
+        <v>58626</v>
+      </c>
+      <c r="B1509" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1509" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1509" t="s">
+        <v>1516</v>
+      </c>
+    </row>
+    <row r="1510" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1510">
+        <v>58902</v>
+      </c>
+      <c r="B1510" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1510" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1510" t="s">
+        <v>1517</v>
+      </c>
+    </row>
+    <row r="1511" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1511">
+        <v>59371</v>
+      </c>
+      <c r="B1511" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1511" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1511" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="1512" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1512">
+        <v>59372</v>
+      </c>
+      <c r="B1512" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1512" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1512" t="s">
+        <v>1519</v>
+      </c>
+    </row>
+    <row r="1513" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1513">
+        <v>59551</v>
+      </c>
+      <c r="B1513" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1513" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1513" t="s">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="1514" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1514">
+        <v>59552</v>
+      </c>
+      <c r="B1514" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1514" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1514" t="s">
+        <v>1521</v>
+      </c>
+    </row>
+    <row r="1515" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1515">
+        <v>60703</v>
+      </c>
+      <c r="B1515" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1515" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1515" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="1516" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1516">
+        <v>61231</v>
+      </c>
+      <c r="B1516" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1516" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1516" t="s">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="1517" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1517">
+        <v>61387</v>
+      </c>
+      <c r="B1517" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1517" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1517" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="1518" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1518">
+        <v>61470</v>
+      </c>
+      <c r="B1518" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1518" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1518" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="1519" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1519">
+        <v>61471</v>
+      </c>
+      <c r="B1519" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1519" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1519" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="1520" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1520">
+        <v>61472</v>
+      </c>
+      <c r="B1520" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1520" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1520" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="1521" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1521">
+        <v>61473</v>
+      </c>
+      <c r="B1521" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1521" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1521" t="s">
+        <v>1528</v>
+      </c>
+    </row>
+    <row r="1522" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1522">
+        <v>61474</v>
+      </c>
+      <c r="B1522" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1522" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1522" t="s">
+        <v>1529</v>
+      </c>
+    </row>
+    <row r="1523" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1523">
+        <v>61503</v>
+      </c>
+      <c r="B1523" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1523" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1523" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="1524" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1524">
+        <v>61504</v>
+      </c>
+      <c r="B1524" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1524" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1524" t="s">
+        <v>1531</v>
+      </c>
+    </row>
+    <row r="1525" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1525">
+        <v>61680</v>
+      </c>
+      <c r="B1525" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1525" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1525" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="1526" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1526">
+        <v>61691</v>
+      </c>
+      <c r="B1526" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1526" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1526" t="s">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="1527" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1527">
+        <v>62378</v>
+      </c>
+      <c r="B1527" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1527" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1527" t="s">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="1528" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1528">
+        <v>62549</v>
+      </c>
+      <c r="B1528" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1528" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1528" t="s">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="1529" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1529">
+        <v>62562</v>
+      </c>
+      <c r="B1529" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1529" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1529" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="1530" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1530">
+        <v>63488</v>
+      </c>
+      <c r="B1530" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1530" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1530" t="s">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="1531" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1531">
+        <v>63604</v>
+      </c>
+      <c r="B1531" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1531" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1531" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="1532" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1532">
+        <v>63605</v>
+      </c>
+      <c r="B1532" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1532" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1532" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="1533" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1533">
+        <v>64604</v>
+      </c>
+      <c r="B1533" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1533" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1533" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="1534" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1534">
+        <v>65516</v>
+      </c>
+      <c r="B1534" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1534" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1534" t="s">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="1535" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1535">
+        <v>65517</v>
+      </c>
+      <c r="B1535" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1535" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1535" t="s">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="1536" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1536">
+        <v>66072</v>
+      </c>
+      <c r="B1536" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1536" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1536" t="s">
+        <v>1543</v>
+      </c>
+    </row>
+    <row r="1537" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1537">
+        <v>66116</v>
+      </c>
+      <c r="B1537" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1537" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1537" t="s">
+        <v>1544</v>
+      </c>
+    </row>
+    <row r="1538" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1538">
+        <v>66117</v>
+      </c>
+      <c r="B1538" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1538" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1538" t="s">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="1539" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1539">
+        <v>67366</v>
+      </c>
+      <c r="B1539" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1539" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1539" t="s">
+        <v>1546</v>
+      </c>
+    </row>
+    <row r="1540" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1540">
+        <v>67947</v>
+      </c>
+      <c r="B1540" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1540" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1540" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="1541" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1541">
+        <v>69038</v>
+      </c>
+      <c r="B1541" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1541" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1541" t="s">
+        <v>1548</v>
+      </c>
+    </row>
+    <row r="1542" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1542">
+        <v>69039</v>
+      </c>
+      <c r="B1542" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1542" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1542" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="1543" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1543">
+        <v>69212</v>
+      </c>
+      <c r="B1543" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1543" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1543" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="1544" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1544">
+        <v>69312</v>
+      </c>
+      <c r="B1544" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1544" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1544" t="s">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="1545" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1545">
+        <v>69408</v>
+      </c>
+      <c r="B1545" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1545" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1545" t="s">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="1546" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1546">
+        <v>69631</v>
+      </c>
+      <c r="B1546" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1546" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1546" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="1547" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1547">
+        <v>69682</v>
+      </c>
+      <c r="B1547" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1547" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1547" t="s">
+        <v>1554</v>
+      </c>
+    </row>
+    <row r="1548" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1548">
+        <v>69683</v>
+      </c>
+      <c r="B1548" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1548" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1548" t="s">
+        <v>1555</v>
+      </c>
+    </row>
+    <row r="1549" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1549">
+        <v>69703</v>
+      </c>
+      <c r="B1549" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1549" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1549" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="1550" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1550">
+        <v>70374</v>
+      </c>
+      <c r="B1550" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1550" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1550" t="s">
+        <v>1557</v>
+      </c>
+    </row>
+    <row r="1551" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1551">
+        <v>70816</v>
+      </c>
+      <c r="B1551" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1551" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1551" t="s">
+        <v>1558</v>
+      </c>
+    </row>
+    <row r="1552" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1552">
+        <v>70843</v>
+      </c>
+      <c r="B1552" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1552" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1552" t="s">
+        <v>1559</v>
+      </c>
+    </row>
+    <row r="1553" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1553">
+        <v>70844</v>
+      </c>
+      <c r="B1553" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1553" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1553" t="s">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="1554" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1554">
+        <v>70845</v>
+      </c>
+      <c r="B1554" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1554" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1554" t="s">
+        <v>1561</v>
+      </c>
+    </row>
+    <row r="1555" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1555">
+        <v>70846</v>
+      </c>
+      <c r="B1555" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1555" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1555" t="s">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="1556" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1556">
+        <v>71070</v>
+      </c>
+      <c r="B1556" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1556" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1556" t="s">
+        <v>1563</v>
+      </c>
+    </row>
+    <row r="1557" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1557">
+        <v>71071</v>
+      </c>
+      <c r="B1557" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1557" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1557" t="s">
+        <v>1564</v>
+      </c>
+    </row>
+    <row r="1558" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1558">
+        <v>71297</v>
+      </c>
+      <c r="B1558" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1558" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1558" t="s">
+        <v>1565</v>
+      </c>
+    </row>
+    <row r="1559" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1559">
+        <v>71298</v>
+      </c>
+      <c r="B1559" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1559" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1559" t="s">
+        <v>1566</v>
+      </c>
+    </row>
+    <row r="1560" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1560">
+        <v>71299</v>
+      </c>
+      <c r="B1560" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1560" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1560" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="1561" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1561">
+        <v>71300</v>
+      </c>
+      <c r="B1561" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1561" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1561" t="s">
+        <v>1568</v>
+      </c>
+    </row>
+    <row r="1562" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1562">
+        <v>71448</v>
+      </c>
+      <c r="B1562" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1562" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1562" t="s">
+        <v>1569</v>
+      </c>
+    </row>
+    <row r="1563" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1563">
+        <v>71561</v>
+      </c>
+      <c r="B1563" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1563" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1563" t="s">
+        <v>1570</v>
+      </c>
+    </row>
+    <row r="1564" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1564">
+        <v>71958</v>
+      </c>
+      <c r="B1564" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1564" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1564" t="s">
+        <v>1571</v>
+      </c>
+    </row>
+    <row r="1565" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1565">
+        <v>72344</v>
+      </c>
+      <c r="B1565" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1565" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1565" t="s">
+        <v>1572</v>
+      </c>
+    </row>
+    <row r="1566" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1566">
+        <v>72345</v>
+      </c>
+      <c r="B1566" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1566" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1566" t="s">
+        <v>1573</v>
+      </c>
+    </row>
+    <row r="1567" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1567">
+        <v>72420</v>
+      </c>
+      <c r="B1567" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1567" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1567" t="s">
+        <v>1574</v>
+      </c>
+    </row>
+    <row r="1568" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1568">
+        <v>72421</v>
+      </c>
+      <c r="B1568" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1568" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1568" t="s">
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="1569" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1569">
+        <v>72553</v>
+      </c>
+      <c r="B1569" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1569" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1569" t="s">
+        <v>1576</v>
+      </c>
+    </row>
+    <row r="1570" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1570">
+        <v>72992</v>
+      </c>
+      <c r="B1570" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1570" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1570" t="s">
+        <v>1577</v>
+      </c>
+    </row>
+    <row r="1571" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1571">
+        <v>73405</v>
+      </c>
+      <c r="B1571" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1571" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1571" t="s">
+        <v>1578</v>
+      </c>
+    </row>
+    <row r="1572" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1572">
+        <v>74000</v>
+      </c>
+      <c r="B1572" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1572" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1572" t="s">
+        <v>1579</v>
+      </c>
+    </row>
+    <row r="1573" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1573">
+        <v>74001</v>
+      </c>
+      <c r="B1573" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1573" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1573" t="s">
+        <v>1580</v>
+      </c>
+    </row>
+    <row r="1574" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1574">
+        <v>74002</v>
+      </c>
+      <c r="B1574" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1574" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1574" t="s">
+        <v>1581</v>
+      </c>
+    </row>
+    <row r="1575" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1575">
+        <v>74003</v>
+      </c>
+      <c r="B1575" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1575" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1575" t="s">
+        <v>1582</v>
+      </c>
+    </row>
+    <row r="1576" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1576">
+        <v>74004</v>
+      </c>
+      <c r="B1576" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1576" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1576" t="s">
+        <v>1583</v>
+      </c>
+    </row>
+    <row r="1577" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1577">
+        <v>74005</v>
+      </c>
+      <c r="B1577" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1577" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1577" t="s">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="1578" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1578">
+        <v>74383</v>
+      </c>
+      <c r="B1578" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1578" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1578" t="s">
+        <v>1585</v>
+      </c>
+    </row>
+    <row r="1579" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1579">
+        <v>74384</v>
+      </c>
+      <c r="B1579" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1579" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1579" t="s">
+        <v>1586</v>
+      </c>
+    </row>
+    <row r="1580" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1580">
+        <v>74385</v>
+      </c>
+      <c r="B1580" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1580" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1580" t="s">
+        <v>1587</v>
+      </c>
+    </row>
+    <row r="1581" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1581">
+        <v>77464</v>
+      </c>
+      <c r="B1581" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1581" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1581" t="s">
+        <v>1588</v>
+      </c>
+    </row>
+    <row r="1582" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1582">
+        <v>77465</v>
+      </c>
+      <c r="B1582" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1582" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1582" t="s">
+        <v>1589</v>
+      </c>
+    </row>
+    <row r="1583" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1583">
+        <v>77537</v>
+      </c>
+      <c r="B1583" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1583" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1583" t="s">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="1584" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1584">
+        <v>77538</v>
+      </c>
+      <c r="B1584" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1584" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1584" t="s">
+        <v>1591</v>
+      </c>
+    </row>
+    <row r="1585" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1585">
+        <v>77939</v>
+      </c>
+      <c r="B1585" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1585" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1585" t="s">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="1586" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1586">
+        <v>77940</v>
+      </c>
+      <c r="B1586" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1586" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1586" t="s">
+        <v>1593</v>
+      </c>
+    </row>
+    <row r="1587" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1587">
+        <v>78674</v>
+      </c>
+      <c r="B1587" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1587" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1587" t="s">
+        <v>1594</v>
+      </c>
+    </row>
+    <row r="1588" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1588">
+        <v>79284</v>
+      </c>
+      <c r="B1588" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1588" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1588" t="s">
+        <v>1595</v>
+      </c>
+    </row>
+    <row r="1589" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1589">
+        <v>79285</v>
+      </c>
+      <c r="B1589" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1589" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1589" t="s">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="1590" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1590">
+        <v>79753</v>
+      </c>
+      <c r="B1590" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1590" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1590" t="s">
+        <v>1597</v>
+      </c>
+    </row>
+    <row r="1591" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1591">
+        <v>80718</v>
+      </c>
+      <c r="B1591" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1591" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1591" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="1592" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1592">
+        <v>80719</v>
+      </c>
+      <c r="B1592" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1592" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1592" t="s">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="1593" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1593">
+        <v>80858</v>
+      </c>
+      <c r="B1593" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1593" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1593" t="s">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="1594" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1594">
+        <v>80859</v>
+      </c>
+      <c r="B1594" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1594" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1594" t="s">
+        <v>1601</v>
+      </c>
+    </row>
+    <row r="1595" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1595">
+        <v>80965</v>
+      </c>
+      <c r="B1595" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1595" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1595" t="s">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="1596" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1596">
+        <v>81071</v>
+      </c>
+      <c r="B1596" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1596" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1596" t="s">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="1597" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1597">
+        <v>81072</v>
+      </c>
+      <c r="B1597" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1597" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1597" t="s">
+        <v>1604</v>
+      </c>
+    </row>
+    <row r="1598" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1598">
+        <v>81073</v>
+      </c>
+      <c r="B1598" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1598" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1598" t="s">
+        <v>1605</v>
+      </c>
+    </row>
+    <row r="1599" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1599">
+        <v>81190</v>
+      </c>
+      <c r="B1599" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1599" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1599" t="s">
+        <v>1606</v>
+      </c>
+    </row>
+    <row r="1600" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1600">
+        <v>81776</v>
+      </c>
+      <c r="B1600" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1600" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1600" t="s">
+        <v>1607</v>
+      </c>
+    </row>
+    <row r="1601" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1601">
+        <v>81777</v>
+      </c>
+      <c r="B1601" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1601" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1601" t="s">
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="1602" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1602">
+        <v>81778</v>
+      </c>
+      <c r="B1602" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1602" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1602" t="s">
+        <v>1609</v>
+      </c>
+    </row>
+    <row r="1603" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1603">
+        <v>81779</v>
+      </c>
+      <c r="B1603" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1603" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1603" t="s">
+        <v>1610</v>
+      </c>
+    </row>
+    <row r="1604" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1604">
+        <v>81976</v>
+      </c>
+      <c r="B1604" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1604" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1604" t="s">
+        <v>1611</v>
+      </c>
+    </row>
+    <row r="1605" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1605">
+        <v>81977</v>
+      </c>
+      <c r="B1605" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1605" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1605" t="s">
+        <v>1612</v>
+      </c>
+    </row>
+    <row r="1606" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1606">
+        <v>82121</v>
+      </c>
+      <c r="B1606" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1606" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1606" t="s">
+        <v>1613</v>
+      </c>
+    </row>
+    <row r="1607" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1607">
+        <v>82245</v>
+      </c>
+      <c r="B1607" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1607" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1607" t="s">
+        <v>1614</v>
+      </c>
+    </row>
+    <row r="1608" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1608">
+        <v>82413</v>
+      </c>
+      <c r="B1608" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1608" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1608" t="s">
+        <v>1615</v>
+      </c>
+    </row>
+    <row r="1609" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1609">
+        <v>82766</v>
+      </c>
+      <c r="B1609" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1609" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1609" t="s">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="1610" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1610">
+        <v>82767</v>
+      </c>
+      <c r="B1610" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1610" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1610" t="s">
+        <v>1617</v>
+      </c>
+    </row>
+    <row r="1611" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1611">
+        <v>82914</v>
+      </c>
+      <c r="B1611" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1611" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1611" t="s">
+        <v>1618</v>
+      </c>
+    </row>
+    <row r="1612" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1612">
+        <v>82915</v>
+      </c>
+      <c r="B1612" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1612" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1612" t="s">
+        <v>1619</v>
+      </c>
+    </row>
+    <row r="1613" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1613">
+        <v>83194</v>
+      </c>
+      <c r="B1613" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1613" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1613" t="s">
+        <v>1620</v>
+      </c>
+    </row>
+    <row r="1614" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1614">
+        <v>83468</v>
+      </c>
+      <c r="B1614" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1614" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1614" t="s">
+        <v>1621</v>
+      </c>
+    </row>
+    <row r="1615" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1615">
+        <v>84021</v>
+      </c>
+      <c r="B1615" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1615" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1615" t="s">
+        <v>1622</v>
+      </c>
+    </row>
+    <row r="1616" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1616">
+        <v>84022</v>
+      </c>
+      <c r="B1616" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1616" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1616" t="s">
+        <v>1623</v>
+      </c>
+    </row>
+    <row r="1617" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1617">
+        <v>84194</v>
+      </c>
+      <c r="B1617" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1617" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1617" t="s">
+        <v>1624</v>
+      </c>
+    </row>
+    <row r="1618" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1618">
+        <v>84378</v>
+      </c>
+      <c r="B1618" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1618" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1618" t="s">
+        <v>1625</v>
+      </c>
+    </row>
+    <row r="1619" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1619">
+        <v>84471</v>
+      </c>
+      <c r="B1619" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1619" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1619" t="s">
+        <v>1626</v>
+      </c>
+    </row>
+    <row r="1620" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1620">
+        <v>84472</v>
+      </c>
+      <c r="B1620" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1620" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1620" t="s">
+        <v>1627</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1621">
+        <v>84473</v>
+      </c>
+      <c r="B1621" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1621" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1621" t="s">
+        <v>1628</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1622">
+        <v>84499</v>
+      </c>
+      <c r="B1622" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1622" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1622" t="s">
+        <v>1629</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1623">
+        <v>84504</v>
+      </c>
+      <c r="B1623" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1623" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1623" t="s">
+        <v>1630</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1624">
+        <v>84567</v>
+      </c>
+      <c r="B1624" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1624" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1624" t="s">
+        <v>1631</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1625">
+        <v>84568</v>
+      </c>
+      <c r="B1625" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1625" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1625" t="s">
+        <v>1632</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1626">
+        <v>84689</v>
+      </c>
+      <c r="B1626" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1626" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1626" t="s">
+        <v>1633</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1627">
+        <v>84690</v>
+      </c>
+      <c r="B1627" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1627" t="s">
+        <v>1634</v>
+      </c>
+      <c r="D1627" t="s">
+        <v>1635</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1628">
+        <v>84701</v>
+      </c>
+      <c r="B1628" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1628" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1628" t="s">
+        <v>1636</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1629">
+        <v>84719</v>
+      </c>
+      <c r="B1629" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1629" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1629" t="s">
+        <v>1637</v>
+      </c>
+    </row>
+    <row r="1630" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1630">
+        <v>84720</v>
+      </c>
+      <c r="B1630" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1630" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1630" t="s">
+        <v>1638</v>
+      </c>
+    </row>
+    <row r="1631" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1631">
+        <v>84861</v>
+      </c>
+      <c r="B1631" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1631" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1631" t="s">
+        <v>1639</v>
+      </c>
+    </row>
+    <row r="1632" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1632">
+        <v>84862</v>
+      </c>
+      <c r="B1632" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1632" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1632" t="s">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1633">
+        <v>85279</v>
+      </c>
+      <c r="B1633" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1633" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1633" t="s">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="1634" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1634">
+        <v>85309</v>
+      </c>
+      <c r="B1634" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1634" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1634" t="s">
+        <v>1642</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1635">
+        <v>85310</v>
+      </c>
+      <c r="B1635" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1635" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1635" t="s">
+        <v>1643</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1636">
+        <v>85374</v>
+      </c>
+      <c r="B1636" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1636" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1636" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1637">
+        <v>85375</v>
+      </c>
+      <c r="B1637" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1637" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1637" t="s">
+        <v>1645</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1638">
+        <v>85425</v>
+      </c>
+      <c r="B1638" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1638" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1638" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1639">
+        <v>85705</v>
+      </c>
+      <c r="B1639" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1639" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1639" t="s">
+        <v>1647</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1640">
+        <v>85728</v>
+      </c>
+      <c r="B1640" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1640" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1640" t="s">
+        <v>1648</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1641">
+        <v>85834</v>
+      </c>
+      <c r="B1641" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1641" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1641" t="s">
+        <v>1649</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1642">
+        <v>85839</v>
+      </c>
+      <c r="B1642" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1642" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1642" t="s">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="1643" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1643">
+        <v>85993</v>
+      </c>
+      <c r="B1643" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1643" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1643" t="s">
+        <v>1651</v>
+      </c>
+    </row>
+    <row r="1644" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1644">
+        <v>86174</v>
+      </c>
+      <c r="B1644" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1644" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1644" t="s">
+        <v>1652</v>
+      </c>
+    </row>
+    <row r="1645" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1645">
+        <v>86175</v>
+      </c>
+      <c r="B1645" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1645" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1645" t="s">
+        <v>1653</v>
+      </c>
+    </row>
+    <row r="1646" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1646">
+        <v>86176</v>
+      </c>
+      <c r="B1646" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1646" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1646" t="s">
+        <v>1654</v>
+      </c>
+    </row>
+    <row r="1647" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1647">
+        <v>86327</v>
+      </c>
+      <c r="B1647" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1647" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1647" t="s">
+        <v>1655</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1648">
+        <v>86372</v>
+      </c>
+      <c r="B1648" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1648" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1648" t="s">
+        <v>1656</v>
+      </c>
+    </row>
+    <row r="1649" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1649">
+        <v>86373</v>
+      </c>
+      <c r="B1649" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1649" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1649" t="s">
+        <v>1657</v>
+      </c>
+    </row>
+    <row r="1650" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1650">
+        <v>86379</v>
+      </c>
+      <c r="B1650" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1650" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1650" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="1651" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1651">
+        <v>86403</v>
+      </c>
+      <c r="B1651" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1651" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1651" t="s">
+        <v>1659</v>
+      </c>
+    </row>
+    <row r="1652" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1652">
+        <v>86404</v>
+      </c>
+      <c r="B1652" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1652" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1652" t="s">
+        <v>1660</v>
+      </c>
+    </row>
+    <row r="1653" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1653">
+        <v>86405</v>
+      </c>
+      <c r="B1653" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1653" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1653" t="s">
+        <v>1661</v>
+      </c>
+    </row>
+    <row r="1654" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1654">
+        <v>86525</v>
+      </c>
+      <c r="B1654" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1654" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1654" t="s">
+        <v>1662</v>
+      </c>
+    </row>
+    <row r="1655" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1655">
+        <v>86528</v>
+      </c>
+      <c r="B1655" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1655" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1655" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1656">
+        <v>86533</v>
+      </c>
+      <c r="B1656" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1656" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1656" t="s">
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1657">
+        <v>86534</v>
+      </c>
+      <c r="B1657" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1657" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1657" t="s">
+        <v>1665</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1658">
+        <v>86545</v>
+      </c>
+      <c r="B1658" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1658" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1658" t="s">
+        <v>1666</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1659">
+        <v>86546</v>
+      </c>
+      <c r="B1659" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1659" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1659" t="s">
+        <v>1667</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1660">
+        <v>86547</v>
+      </c>
+      <c r="B1660" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1660" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1660" t="s">
+        <v>1668</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1661">
+        <v>86633</v>
+      </c>
+      <c r="B1661" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1661" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1661" t="s">
+        <v>1669</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1662">
+        <v>86750</v>
+      </c>
+      <c r="B1662" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1662" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1662" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1663">
+        <v>86751</v>
+      </c>
+      <c r="B1663" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1663" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1663" t="s">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="1664" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1664">
+        <v>86771</v>
+      </c>
+      <c r="B1664" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1664" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1664" t="s">
+        <v>1672</v>
+      </c>
+    </row>
+    <row r="1665" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1665">
+        <v>86772</v>
+      </c>
+      <c r="B1665" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1665" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1665" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="1666" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1666">
+        <v>86814</v>
+      </c>
+      <c r="B1666" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1666" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1666" t="s">
+        <v>1674</v>
+      </c>
+    </row>
+    <row r="1667" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1667">
+        <v>86916</v>
+      </c>
+      <c r="B1667" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1667" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1667" t="s">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="1668" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1668">
+        <v>86917</v>
+      </c>
+      <c r="B1668" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1668" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1668" t="s">
+        <v>1676</v>
+      </c>
+    </row>
+    <row r="1669" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1669">
+        <v>86918</v>
+      </c>
+      <c r="B1669" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1669" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1669" t="s">
+        <v>1677</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/apps/backend/excel-data/issuereturn_library_migration.xlsx
+++ b/apps/backend/excel-data/issuereturn_library_migration.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5008" uniqueCount="1678">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5098" uniqueCount="1708">
   <si>
     <t>legacy_id</t>
   </si>
@@ -5046,6 +5046,96 @@
   </si>
   <si>
     <t>2026-05-11T08:00:15.126Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T08:00:52.949Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T08:01:30.230Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T08:01:37.829Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T08:01:42.079Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T08:01:54.274Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T08:01:56.857Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T08:02:08.990Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T08:02:10.729Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T08:02:12.261Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T08:02:13.850Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T08:02:21.129Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T08:02:35.592Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T08:02:42.941Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T08:02:49.287Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T08:02:51.584Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T08:02:53.209Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T08:02:54.418Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T08:02:55.487Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T08:03:02.392Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T08:03:15.135Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T08:03:22.745Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T08:03:29.350Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T08:03:38.296Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T08:03:45.798Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T08:03:54.169Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T08:03:56.217Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T08:03:57.481Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T08:03:59.465Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T08:04:00.978Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T08:04:02.152Z</t>
   </si>
 </sst>
 </file>
@@ -5426,7 +5516,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1669"/>
+  <dimension ref="A1:D1699"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -28795,6 +28885,426 @@
         <v>1677</v>
       </c>
     </row>
+    <row r="1670" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1670">
+        <v>86919</v>
+      </c>
+      <c r="B1670" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1670" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1670" t="s">
+        <v>1678</v>
+      </c>
+    </row>
+    <row r="1671" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1671">
+        <v>87072</v>
+      </c>
+      <c r="B1671" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1671" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1671" t="s">
+        <v>1679</v>
+      </c>
+    </row>
+    <row r="1672" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1672">
+        <v>87365</v>
+      </c>
+      <c r="B1672" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1672" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1672" t="s">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="1673" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1673">
+        <v>87366</v>
+      </c>
+      <c r="B1673" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1673" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1673" t="s">
+        <v>1681</v>
+      </c>
+    </row>
+    <row r="1674" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1674">
+        <v>87405</v>
+      </c>
+      <c r="B1674" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1674" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1674" t="s">
+        <v>1682</v>
+      </c>
+    </row>
+    <row r="1675" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1675">
+        <v>87406</v>
+      </c>
+      <c r="B1675" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1675" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1675" t="s">
+        <v>1683</v>
+      </c>
+    </row>
+    <row r="1676" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1676">
+        <v>87407</v>
+      </c>
+      <c r="B1676" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1676" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1676" t="s">
+        <v>1684</v>
+      </c>
+    </row>
+    <row r="1677" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1677">
+        <v>87532</v>
+      </c>
+      <c r="B1677" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1677" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1677" t="s">
+        <v>1685</v>
+      </c>
+    </row>
+    <row r="1678" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1678">
+        <v>87533</v>
+      </c>
+      <c r="B1678" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1678" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1678" t="s">
+        <v>1686</v>
+      </c>
+    </row>
+    <row r="1679" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1679">
+        <v>87534</v>
+      </c>
+      <c r="B1679" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1679" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1679" t="s">
+        <v>1687</v>
+      </c>
+    </row>
+    <row r="1680" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1680">
+        <v>87558</v>
+      </c>
+      <c r="B1680" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1680" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1680" t="s">
+        <v>1688</v>
+      </c>
+    </row>
+    <row r="1681" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1681">
+        <v>87580</v>
+      </c>
+      <c r="B1681" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1681" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1681" t="s">
+        <v>1689</v>
+      </c>
+    </row>
+    <row r="1682" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1682">
+        <v>87674</v>
+      </c>
+      <c r="B1682" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1682" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1682" t="s">
+        <v>1690</v>
+      </c>
+    </row>
+    <row r="1683" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1683">
+        <v>87731</v>
+      </c>
+      <c r="B1683" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1683" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1683" t="s">
+        <v>1691</v>
+      </c>
+    </row>
+    <row r="1684" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1684">
+        <v>87745</v>
+      </c>
+      <c r="B1684" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1684" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1684" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1685" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1685">
+        <v>87746</v>
+      </c>
+      <c r="B1685" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1685" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1685" t="s">
+        <v>1693</v>
+      </c>
+    </row>
+    <row r="1686" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1686">
+        <v>87747</v>
+      </c>
+      <c r="B1686" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1686" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1686" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="1687" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1687">
+        <v>87748</v>
+      </c>
+      <c r="B1687" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1687" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1687" t="s">
+        <v>1695</v>
+      </c>
+    </row>
+    <row r="1688" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1688">
+        <v>87753</v>
+      </c>
+      <c r="B1688" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1688" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1688" t="s">
+        <v>1696</v>
+      </c>
+    </row>
+    <row r="1689" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1689">
+        <v>87800</v>
+      </c>
+      <c r="B1689" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1689" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1689" t="s">
+        <v>1697</v>
+      </c>
+    </row>
+    <row r="1690" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1690">
+        <v>87801</v>
+      </c>
+      <c r="B1690" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1690" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1690" t="s">
+        <v>1698</v>
+      </c>
+    </row>
+    <row r="1691" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1691">
+        <v>87802</v>
+      </c>
+      <c r="B1691" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1691" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1691" t="s">
+        <v>1699</v>
+      </c>
+    </row>
+    <row r="1692" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1692">
+        <v>88131</v>
+      </c>
+      <c r="B1692" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1692" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1692" t="s">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="1693" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1693">
+        <v>88132</v>
+      </c>
+      <c r="B1693" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1693" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1693" t="s">
+        <v>1701</v>
+      </c>
+    </row>
+    <row r="1694" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1694">
+        <v>88280</v>
+      </c>
+      <c r="B1694" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1694" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1694" t="s">
+        <v>1702</v>
+      </c>
+    </row>
+    <row r="1695" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1695">
+        <v>88317</v>
+      </c>
+      <c r="B1695" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1695" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1695" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="1696" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1696">
+        <v>88318</v>
+      </c>
+      <c r="B1696" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1696" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1696" t="s">
+        <v>1704</v>
+      </c>
+    </row>
+    <row r="1697" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1697">
+        <v>88373</v>
+      </c>
+      <c r="B1697" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1697" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1697" t="s">
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="1698" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1698">
+        <v>88381</v>
+      </c>
+      <c r="B1698" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1698" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1698" t="s">
+        <v>1706</v>
+      </c>
+    </row>
+    <row r="1699" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1699">
+        <v>88382</v>
+      </c>
+      <c r="B1699" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1699" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1699" t="s">
+        <v>1707</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
